--- a/excel/1000(n)/RAW_Dataset.xlsx
+++ b/excel/1000(n)/RAW_Dataset.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\#Java-Practice\##SS2\Lab3 Sorting\excel\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t xml:space="preserve">Algorithm </t>
   </si>
@@ -58,12 +58,316 @@
   </si>
   <si>
     <t>Trial 9</t>
+  </si>
+  <si>
+    <t>Bubble Sort</t>
+  </si>
+  <si>
+    <t>Bubble Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Insertion Sort</t>
+  </si>
+  <si>
+    <t>Insertion Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Selection Sort</t>
+  </si>
+  <si>
+    <t>Selection Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Merge Sort</t>
+  </si>
+  <si>
+    <t>Merge Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Quick Sort</t>
+  </si>
+  <si>
+    <t>Quick Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Trial 10</t>
+  </si>
+  <si>
+    <t>Trial 11</t>
+  </si>
+  <si>
+    <t>Trial 12</t>
+  </si>
+  <si>
+    <t>Trial 13</t>
+  </si>
+  <si>
+    <t>Trial 14</t>
+  </si>
+  <si>
+    <t>Trial 15</t>
+  </si>
+  <si>
+    <t>Trial 16</t>
+  </si>
+  <si>
+    <t>Trial 17</t>
+  </si>
+  <si>
+    <t>Trial 18</t>
+  </si>
+  <si>
+    <t>Trial 19</t>
+  </si>
+  <si>
+    <t>Trial 20</t>
+  </si>
+  <si>
+    <t>Trial 21</t>
+  </si>
+  <si>
+    <t>Trial 22</t>
+  </si>
+  <si>
+    <t>Trial 23</t>
+  </si>
+  <si>
+    <t>Trial 24</t>
+  </si>
+  <si>
+    <t>Trial 25</t>
+  </si>
+  <si>
+    <t>Trial 26</t>
+  </si>
+  <si>
+    <t>Trial 27</t>
+  </si>
+  <si>
+    <t>Trial 28</t>
+  </si>
+  <si>
+    <t>Trial 29</t>
+  </si>
+  <si>
+    <t>Trial 30</t>
+  </si>
+  <si>
+    <t>Trial 31</t>
+  </si>
+  <si>
+    <t>Trial 32</t>
+  </si>
+  <si>
+    <t>Trial 33</t>
+  </si>
+  <si>
+    <t>Trial 34</t>
+  </si>
+  <si>
+    <t>Trial 35</t>
+  </si>
+  <si>
+    <t>Trial 36</t>
+  </si>
+  <si>
+    <t>Trial 37</t>
+  </si>
+  <si>
+    <t>Trial 38</t>
+  </si>
+  <si>
+    <t>Trial 39</t>
+  </si>
+  <si>
+    <t>Trial 40</t>
+  </si>
+  <si>
+    <t>Trial 41</t>
+  </si>
+  <si>
+    <t>Trial 42</t>
+  </si>
+  <si>
+    <t>Trial 43</t>
+  </si>
+  <si>
+    <t>Trial 44</t>
+  </si>
+  <si>
+    <t>Trial 45</t>
+  </si>
+  <si>
+    <t>Trial 46</t>
+  </si>
+  <si>
+    <t>Trial 47</t>
+  </si>
+  <si>
+    <t>Trial 48</t>
+  </si>
+  <si>
+    <t>Trial 49</t>
+  </si>
+  <si>
+    <t>Trial 50</t>
+  </si>
+  <si>
+    <t>Trial 51</t>
+  </si>
+  <si>
+    <t>Trial 52</t>
+  </si>
+  <si>
+    <t>Trial 53</t>
+  </si>
+  <si>
+    <t>Trial 54</t>
+  </si>
+  <si>
+    <t>Trial 55</t>
+  </si>
+  <si>
+    <t>Trial 56</t>
+  </si>
+  <si>
+    <t>Trial 57</t>
+  </si>
+  <si>
+    <t>Trial 58</t>
+  </si>
+  <si>
+    <t>Trial 59</t>
+  </si>
+  <si>
+    <t>Trial 60</t>
+  </si>
+  <si>
+    <t>Trial 61</t>
+  </si>
+  <si>
+    <t>Trial 62</t>
+  </si>
+  <si>
+    <t>Trial 63</t>
+  </si>
+  <si>
+    <t>Trial 64</t>
+  </si>
+  <si>
+    <t>Trial 65</t>
+  </si>
+  <si>
+    <t>Trial 66</t>
+  </si>
+  <si>
+    <t>Trial 67</t>
+  </si>
+  <si>
+    <t>Trial 68</t>
+  </si>
+  <si>
+    <t>Trial 69</t>
+  </si>
+  <si>
+    <t>Trial 70</t>
+  </si>
+  <si>
+    <t>Trial 71</t>
+  </si>
+  <si>
+    <t>Trial 72</t>
+  </si>
+  <si>
+    <t>Trial 73</t>
+  </si>
+  <si>
+    <t>Trial 74</t>
+  </si>
+  <si>
+    <t>Trial 75</t>
+  </si>
+  <si>
+    <t>Trial 76</t>
+  </si>
+  <si>
+    <t>Trial 77</t>
+  </si>
+  <si>
+    <t>Trial 78</t>
+  </si>
+  <si>
+    <t>Trial 79</t>
+  </si>
+  <si>
+    <t>Trial 80</t>
+  </si>
+  <si>
+    <t>Trial 81</t>
+  </si>
+  <si>
+    <t>Trial 82</t>
+  </si>
+  <si>
+    <t>Trial 83</t>
+  </si>
+  <si>
+    <t>Trial 84</t>
+  </si>
+  <si>
+    <t>Trial 85</t>
+  </si>
+  <si>
+    <t>Trial 86</t>
+  </si>
+  <si>
+    <t>Trial 87</t>
+  </si>
+  <si>
+    <t>Trial 88</t>
+  </si>
+  <si>
+    <t>Trial 89</t>
+  </si>
+  <si>
+    <t>Trial 90</t>
+  </si>
+  <si>
+    <t>Trial 91</t>
+  </si>
+  <si>
+    <t>Trial 92</t>
+  </si>
+  <si>
+    <t>Trial 93</t>
+  </si>
+  <si>
+    <t>Trial 94</t>
+  </si>
+  <si>
+    <t>Trial 95</t>
+  </si>
+  <si>
+    <t>Trial 96</t>
+  </si>
+  <si>
+    <t>Trial 97</t>
+  </si>
+  <si>
+    <t>Trial 98</t>
+  </si>
+  <si>
+    <t>Trial 99</t>
+  </si>
+  <si>
+    <t>Trial 100</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -388,11 +692,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:CX11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.77734375" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="14.77734375"/>
+    <col min="2" max="2" customWidth="true" width="13.33203125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.5">
@@ -402,32 +706,3385 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" t="s" s="0">
         <v>10</v>
+      </c>
+      <c r="L1" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="P1" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="Q1" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="R1" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="S1" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="T1" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="U1" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="V1" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="W1" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="X1" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="Y1" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="Z1" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="AA1" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="AB1" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="AC1" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="AD1" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="AE1" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="AF1" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="AG1" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="AH1" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="AI1" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="AJ1" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="AK1" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="AL1" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="AM1" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="AN1" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="AO1" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="AP1" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="AQ1" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="AR1" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="AS1" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="AT1" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="AU1" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="AV1" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="AW1" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="AX1" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="AY1" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="AZ1" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="BA1" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="BB1" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="BC1" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="BD1" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="BE1" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="BF1" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="BG1" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="BH1" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="BI1" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="BJ1" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="BK1" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="BL1" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="BM1" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="BN1" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="BO1" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="BP1" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="BQ1" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="BR1" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="BS1" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BT1" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="BU1" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="BV1" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="BW1" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="BX1" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="BY1" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="BZ1" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="CA1" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="CB1" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="CC1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="CD1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="CE1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="CF1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="CG1" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="CH1" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="CI1" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="CJ1" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="CK1" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="CL1" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="CM1" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="CN1" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="CO1" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="CP1" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="CQ1" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="CR1" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="CS1" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="CT1" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="CU1" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="CV1" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="CW1" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="CX1" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B2" t="n" s="0">
+        <v>1000.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>4591000.0</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>2564400.0</v>
+      </c>
+      <c r="E2" t="n" s="0">
+        <v>1753800.0</v>
+      </c>
+      <c r="F2" t="n" s="0">
+        <v>782400.0</v>
+      </c>
+      <c r="G2" t="n" s="0">
+        <v>700500.0</v>
+      </c>
+      <c r="H2" t="n" s="0">
+        <v>1255400.0</v>
+      </c>
+      <c r="I2" t="n" s="0">
+        <v>557500.0</v>
+      </c>
+      <c r="J2" t="n" s="0">
+        <v>571800.0</v>
+      </c>
+      <c r="K2" t="n" s="0">
+        <v>586900.0</v>
+      </c>
+      <c r="L2" t="n" s="0">
+        <v>561300.0</v>
+      </c>
+      <c r="M2" t="n" s="0">
+        <v>594400.0</v>
+      </c>
+      <c r="N2" t="n" s="0">
+        <v>561100.0</v>
+      </c>
+      <c r="O2" t="n" s="0">
+        <v>572700.0</v>
+      </c>
+      <c r="P2" t="n" s="0">
+        <v>570600.0</v>
+      </c>
+      <c r="Q2" t="n" s="0">
+        <v>570400.0</v>
+      </c>
+      <c r="R2" t="n" s="0">
+        <v>589200.0</v>
+      </c>
+      <c r="S2" t="n" s="0">
+        <v>575100.0</v>
+      </c>
+      <c r="T2" t="n" s="0">
+        <v>1223300.0</v>
+      </c>
+      <c r="U2" t="n" s="0">
+        <v>603200.0</v>
+      </c>
+      <c r="V2" t="n" s="0">
+        <v>587200.0</v>
+      </c>
+      <c r="W2" t="n" s="0">
+        <v>577900.0</v>
+      </c>
+      <c r="X2" t="n" s="0">
+        <v>749900.0</v>
+      </c>
+      <c r="Y2" t="n" s="0">
+        <v>560600.0</v>
+      </c>
+      <c r="Z2" t="n" s="0">
+        <v>585100.0</v>
+      </c>
+      <c r="AA2" t="n" s="0">
+        <v>587200.0</v>
+      </c>
+      <c r="AB2" t="n" s="0">
+        <v>1075900.0</v>
+      </c>
+      <c r="AC2" t="n" s="0">
+        <v>597300.0</v>
+      </c>
+      <c r="AD2" t="n" s="0">
+        <v>581300.0</v>
+      </c>
+      <c r="AE2" t="n" s="0">
+        <v>628600.0</v>
+      </c>
+      <c r="AF2" t="n" s="0">
+        <v>620800.0</v>
+      </c>
+      <c r="AG2" t="n" s="0">
+        <v>588200.0</v>
+      </c>
+      <c r="AH2" t="n" s="0">
+        <v>571600.0</v>
+      </c>
+      <c r="AI2" t="n" s="0">
+        <v>558300.0</v>
+      </c>
+      <c r="AJ2" t="n" s="0">
+        <v>622900.0</v>
+      </c>
+      <c r="AK2" t="n" s="0">
+        <v>577400.0</v>
+      </c>
+      <c r="AL2" t="n" s="0">
+        <v>557800.0</v>
+      </c>
+      <c r="AM2" t="n" s="0">
+        <v>1153400.0</v>
+      </c>
+      <c r="AN2" t="n" s="0">
+        <v>598400.0</v>
+      </c>
+      <c r="AO2" t="n" s="0">
+        <v>569400.0</v>
+      </c>
+      <c r="AP2" t="n" s="0">
+        <v>556900.0</v>
+      </c>
+      <c r="AQ2" t="n" s="0">
+        <v>572400.0</v>
+      </c>
+      <c r="AR2" t="n" s="0">
+        <v>592500.0</v>
+      </c>
+      <c r="AS2" t="n" s="0">
+        <v>610600.0</v>
+      </c>
+      <c r="AT2" t="n" s="0">
+        <v>603600.0</v>
+      </c>
+      <c r="AU2" t="n" s="0">
+        <v>574800.0</v>
+      </c>
+      <c r="AV2" t="n" s="0">
+        <v>583900.0</v>
+      </c>
+      <c r="AW2" t="n" s="0">
+        <v>578600.0</v>
+      </c>
+      <c r="AX2" t="n" s="0">
+        <v>609000.0</v>
+      </c>
+      <c r="AY2" t="n" s="0">
+        <v>584600.0</v>
+      </c>
+      <c r="AZ2" t="n" s="0">
+        <v>577100.0</v>
+      </c>
+      <c r="BA2" t="n" s="0">
+        <v>576900.0</v>
+      </c>
+      <c r="BB2" t="n" s="0">
+        <v>563800.0</v>
+      </c>
+      <c r="BC2" t="n" s="0">
+        <v>592200.0</v>
+      </c>
+      <c r="BD2" t="n" s="0">
+        <v>585800.0</v>
+      </c>
+      <c r="BE2" t="n" s="0">
+        <v>574700.0</v>
+      </c>
+      <c r="BF2" t="n" s="0">
+        <v>595900.0</v>
+      </c>
+      <c r="BG2" t="n" s="0">
+        <v>565600.0</v>
+      </c>
+      <c r="BH2" t="n" s="0">
+        <v>574900.0</v>
+      </c>
+      <c r="BI2" t="n" s="0">
+        <v>562200.0</v>
+      </c>
+      <c r="BJ2" t="n" s="0">
+        <v>575900.0</v>
+      </c>
+      <c r="BK2" t="n" s="0">
+        <v>576200.0</v>
+      </c>
+      <c r="BL2" t="n" s="0">
+        <v>594600.0</v>
+      </c>
+      <c r="BM2" t="n" s="0">
+        <v>596800.0</v>
+      </c>
+      <c r="BN2" t="n" s="0">
+        <v>915600.0</v>
+      </c>
+      <c r="BO2" t="n" s="0">
+        <v>614000.0</v>
+      </c>
+      <c r="BP2" t="n" s="0">
+        <v>574100.0</v>
+      </c>
+      <c r="BQ2" t="n" s="0">
+        <v>583000.0</v>
+      </c>
+      <c r="BR2" t="n" s="0">
+        <v>601200.0</v>
+      </c>
+      <c r="BS2" t="n" s="0">
+        <v>597400.0</v>
+      </c>
+      <c r="BT2" t="n" s="0">
+        <v>613100.0</v>
+      </c>
+      <c r="BU2" t="n" s="0">
+        <v>605500.0</v>
+      </c>
+      <c r="BV2" t="n" s="0">
+        <v>586700.0</v>
+      </c>
+      <c r="BW2" t="n" s="0">
+        <v>569700.0</v>
+      </c>
+      <c r="BX2" t="n" s="0">
+        <v>583500.0</v>
+      </c>
+      <c r="BY2" t="n" s="0">
+        <v>1006400.0</v>
+      </c>
+      <c r="BZ2" t="n" s="0">
+        <v>576600.0</v>
+      </c>
+      <c r="CA2" t="n" s="0">
+        <v>572400.0</v>
+      </c>
+      <c r="CB2" t="n" s="0">
+        <v>586600.0</v>
+      </c>
+      <c r="CC2" t="n" s="0">
+        <v>568900.0</v>
+      </c>
+      <c r="CD2" t="n" s="0">
+        <v>586800.0</v>
+      </c>
+      <c r="CE2" t="n" s="0">
+        <v>610100.0</v>
+      </c>
+      <c r="CF2" t="n" s="0">
+        <v>560900.0</v>
+      </c>
+      <c r="CG2" t="n" s="0">
+        <v>603900.0</v>
+      </c>
+      <c r="CH2" t="n" s="0">
+        <v>570300.0</v>
+      </c>
+      <c r="CI2" t="n" s="0">
+        <v>597800.0</v>
+      </c>
+      <c r="CJ2" t="n" s="0">
+        <v>571500.0</v>
+      </c>
+      <c r="CK2" t="n" s="0">
+        <v>581400.0</v>
+      </c>
+      <c r="CL2" t="n" s="0">
+        <v>590600.0</v>
+      </c>
+      <c r="CM2" t="n" s="0">
+        <v>591000.0</v>
+      </c>
+      <c r="CN2" t="n" s="0">
+        <v>582200.0</v>
+      </c>
+      <c r="CO2" t="n" s="0">
+        <v>588600.0</v>
+      </c>
+      <c r="CP2" t="n" s="0">
+        <v>691000.0</v>
+      </c>
+      <c r="CQ2" t="n" s="0">
+        <v>573500.0</v>
+      </c>
+      <c r="CR2" t="n" s="0">
+        <v>575700.0</v>
+      </c>
+      <c r="CS2" t="n" s="0">
+        <v>691000.0</v>
+      </c>
+      <c r="CT2" t="n" s="0">
+        <v>620800.0</v>
+      </c>
+      <c r="CU2" t="n" s="0">
+        <v>596400.0</v>
+      </c>
+      <c r="CV2" t="n" s="0">
+        <v>609900.0</v>
+      </c>
+      <c r="CW2" t="n" s="0">
+        <v>580000.0</v>
+      </c>
+      <c r="CX2" t="n" s="0">
+        <v>566300.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B3" t="n" s="0">
+        <v>1000.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>4196300.0</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>602700.0</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>898500.0</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>1116600.0</v>
+      </c>
+      <c r="G3" t="n" s="0">
+        <v>595000.0</v>
+      </c>
+      <c r="H3" t="n" s="0">
+        <v>1010000.0</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>575400.0</v>
+      </c>
+      <c r="J3" t="n" s="0">
+        <v>941800.0</v>
+      </c>
+      <c r="K3" t="n" s="0">
+        <v>656700.0</v>
+      </c>
+      <c r="L3" t="n" s="0">
+        <v>734300.0</v>
+      </c>
+      <c r="M3" t="n" s="0">
+        <v>713800.0</v>
+      </c>
+      <c r="N3" t="n" s="0">
+        <v>743900.0</v>
+      </c>
+      <c r="O3" t="n" s="0">
+        <v>700600.0</v>
+      </c>
+      <c r="P3" t="n" s="0">
+        <v>740900.0</v>
+      </c>
+      <c r="Q3" t="n" s="0">
+        <v>712900.0</v>
+      </c>
+      <c r="R3" t="n" s="0">
+        <v>705000.0</v>
+      </c>
+      <c r="S3" t="n" s="0">
+        <v>728500.0</v>
+      </c>
+      <c r="T3" t="n" s="0">
+        <v>1217600.0</v>
+      </c>
+      <c r="U3" t="n" s="0">
+        <v>782000.0</v>
+      </c>
+      <c r="V3" t="n" s="0">
+        <v>704300.0</v>
+      </c>
+      <c r="W3" t="n" s="0">
+        <v>740900.0</v>
+      </c>
+      <c r="X3" t="n" s="0">
+        <v>813100.0</v>
+      </c>
+      <c r="Y3" t="n" s="0">
+        <v>737700.0</v>
+      </c>
+      <c r="Z3" t="n" s="0">
+        <v>717900.0</v>
+      </c>
+      <c r="AA3" t="n" s="0">
+        <v>718700.0</v>
+      </c>
+      <c r="AB3" t="n" s="0">
+        <v>1514700.0</v>
+      </c>
+      <c r="AC3" t="n" s="0">
+        <v>747100.0</v>
+      </c>
+      <c r="AD3" t="n" s="0">
+        <v>882300.0</v>
+      </c>
+      <c r="AE3" t="n" s="0">
+        <v>705600.0</v>
+      </c>
+      <c r="AF3" t="n" s="0">
+        <v>727200.0</v>
+      </c>
+      <c r="AG3" t="n" s="0">
+        <v>735800.0</v>
+      </c>
+      <c r="AH3" t="n" s="0">
+        <v>809200.0</v>
+      </c>
+      <c r="AI3" t="n" s="0">
+        <v>739500.0</v>
+      </c>
+      <c r="AJ3" t="n" s="0">
+        <v>767800.0</v>
+      </c>
+      <c r="AK3" t="n" s="0">
+        <v>726200.0</v>
+      </c>
+      <c r="AL3" t="n" s="0">
+        <v>745800.0</v>
+      </c>
+      <c r="AM3" t="n" s="0">
+        <v>1277400.0</v>
+      </c>
+      <c r="AN3" t="n" s="0">
+        <v>780400.0</v>
+      </c>
+      <c r="AO3" t="n" s="0">
+        <v>784300.0</v>
+      </c>
+      <c r="AP3" t="n" s="0">
+        <v>713100.0</v>
+      </c>
+      <c r="AQ3" t="n" s="0">
+        <v>745100.0</v>
+      </c>
+      <c r="AR3" t="n" s="0">
+        <v>706900.0</v>
+      </c>
+      <c r="AS3" t="n" s="0">
+        <v>772700.0</v>
+      </c>
+      <c r="AT3" t="n" s="0">
+        <v>778900.0</v>
+      </c>
+      <c r="AU3" t="n" s="0">
+        <v>724600.0</v>
+      </c>
+      <c r="AV3" t="n" s="0">
+        <v>768800.0</v>
+      </c>
+      <c r="AW3" t="n" s="0">
+        <v>714600.0</v>
+      </c>
+      <c r="AX3" t="n" s="0">
+        <v>773200.0</v>
+      </c>
+      <c r="AY3" t="n" s="0">
+        <v>712400.0</v>
+      </c>
+      <c r="AZ3" t="n" s="0">
+        <v>725500.0</v>
+      </c>
+      <c r="BA3" t="n" s="0">
+        <v>713200.0</v>
+      </c>
+      <c r="BB3" t="n" s="0">
+        <v>721000.0</v>
+      </c>
+      <c r="BC3" t="n" s="0">
+        <v>743100.0</v>
+      </c>
+      <c r="BD3" t="n" s="0">
+        <v>716300.0</v>
+      </c>
+      <c r="BE3" t="n" s="0">
+        <v>695400.0</v>
+      </c>
+      <c r="BF3" t="n" s="0">
+        <v>790900.0</v>
+      </c>
+      <c r="BG3" t="n" s="0">
+        <v>767700.0</v>
+      </c>
+      <c r="BH3" t="n" s="0">
+        <v>732400.0</v>
+      </c>
+      <c r="BI3" t="n" s="0">
+        <v>706900.0</v>
+      </c>
+      <c r="BJ3" t="n" s="0">
+        <v>722900.0</v>
+      </c>
+      <c r="BK3" t="n" s="0">
+        <v>934300.0</v>
+      </c>
+      <c r="BL3" t="n" s="0">
+        <v>857200.0</v>
+      </c>
+      <c r="BM3" t="n" s="0">
+        <v>716500.0</v>
+      </c>
+      <c r="BN3" t="n" s="0">
+        <v>716500.0</v>
+      </c>
+      <c r="BO3" t="n" s="0">
+        <v>724900.0</v>
+      </c>
+      <c r="BP3" t="n" s="0">
+        <v>720000.0</v>
+      </c>
+      <c r="BQ3" t="n" s="0">
+        <v>704700.0</v>
+      </c>
+      <c r="BR3" t="n" s="0">
+        <v>717200.0</v>
+      </c>
+      <c r="BS3" t="n" s="0">
+        <v>712700.0</v>
+      </c>
+      <c r="BT3" t="n" s="0">
+        <v>836500.0</v>
+      </c>
+      <c r="BU3" t="n" s="0">
+        <v>707500.0</v>
+      </c>
+      <c r="BV3" t="n" s="0">
+        <v>716200.0</v>
+      </c>
+      <c r="BW3" t="n" s="0">
+        <v>774700.0</v>
+      </c>
+      <c r="BX3" t="n" s="0">
+        <v>708000.0</v>
+      </c>
+      <c r="BY3" t="n" s="0">
+        <v>721700.0</v>
+      </c>
+      <c r="BZ3" t="n" s="0">
+        <v>758800.0</v>
+      </c>
+      <c r="CA3" t="n" s="0">
+        <v>691900.0</v>
+      </c>
+      <c r="CB3" t="n" s="0">
+        <v>694500.0</v>
+      </c>
+      <c r="CC3" t="n" s="0">
+        <v>714100.0</v>
+      </c>
+      <c r="CD3" t="n" s="0">
+        <v>708600.0</v>
+      </c>
+      <c r="CE3" t="n" s="0">
+        <v>829800.0</v>
+      </c>
+      <c r="CF3" t="n" s="0">
+        <v>834800.0</v>
+      </c>
+      <c r="CG3" t="n" s="0">
+        <v>823900.0</v>
+      </c>
+      <c r="CH3" t="n" s="0">
+        <v>759000.0</v>
+      </c>
+      <c r="CI3" t="n" s="0">
+        <v>735100.0</v>
+      </c>
+      <c r="CJ3" t="n" s="0">
+        <v>859500.0</v>
+      </c>
+      <c r="CK3" t="n" s="0">
+        <v>737500.0</v>
+      </c>
+      <c r="CL3" t="n" s="0">
+        <v>757800.0</v>
+      </c>
+      <c r="CM3" t="n" s="0">
+        <v>744400.0</v>
+      </c>
+      <c r="CN3" t="n" s="0">
+        <v>739400.0</v>
+      </c>
+      <c r="CO3" t="n" s="0">
+        <v>734300.0</v>
+      </c>
+      <c r="CP3" t="n" s="0">
+        <v>739400.0</v>
+      </c>
+      <c r="CQ3" t="n" s="0">
+        <v>734700.0</v>
+      </c>
+      <c r="CR3" t="n" s="0">
+        <v>734100.0</v>
+      </c>
+      <c r="CS3" t="n" s="0">
+        <v>692500.0</v>
+      </c>
+      <c r="CT3" t="n" s="0">
+        <v>798100.0</v>
+      </c>
+      <c r="CU3" t="n" s="0">
+        <v>774200.0</v>
+      </c>
+      <c r="CV3" t="n" s="0">
+        <v>728900.0</v>
+      </c>
+      <c r="CW3" t="n" s="0">
+        <v>734400.0</v>
+      </c>
+      <c r="CX3" t="n" s="0">
+        <v>751600.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>1000.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>1422500.0</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>3280100.0</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>286500.0</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>98200.0</v>
+      </c>
+      <c r="G4" t="n" s="0">
+        <v>46700.0</v>
+      </c>
+      <c r="H4" t="n" s="0">
+        <v>75400.0</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>46000.0</v>
+      </c>
+      <c r="J4" t="n" s="0">
+        <v>86900.0</v>
+      </c>
+      <c r="K4" t="n" s="0">
+        <v>47000.0</v>
+      </c>
+      <c r="L4" t="n" s="0">
+        <v>45800.0</v>
+      </c>
+      <c r="M4" t="n" s="0">
+        <v>46100.0</v>
+      </c>
+      <c r="N4" t="n" s="0">
+        <v>46300.0</v>
+      </c>
+      <c r="O4" t="n" s="0">
+        <v>46200.0</v>
+      </c>
+      <c r="P4" t="n" s="0">
+        <v>48200.0</v>
+      </c>
+      <c r="Q4" t="n" s="0">
+        <v>43500.0</v>
+      </c>
+      <c r="R4" t="n" s="0">
+        <v>45800.0</v>
+      </c>
+      <c r="S4" t="n" s="0">
+        <v>45500.0</v>
+      </c>
+      <c r="T4" t="n" s="0">
+        <v>91500.0</v>
+      </c>
+      <c r="U4" t="n" s="0">
+        <v>54000.0</v>
+      </c>
+      <c r="V4" t="n" s="0">
+        <v>47100.0</v>
+      </c>
+      <c r="W4" t="n" s="0">
+        <v>45200.0</v>
+      </c>
+      <c r="X4" t="n" s="0">
+        <v>45500.0</v>
+      </c>
+      <c r="Y4" t="n" s="0">
+        <v>45600.0</v>
+      </c>
+      <c r="Z4" t="n" s="0">
+        <v>46500.0</v>
+      </c>
+      <c r="AA4" t="n" s="0">
+        <v>45900.0</v>
+      </c>
+      <c r="AB4" t="n" s="0">
+        <v>111000.0</v>
+      </c>
+      <c r="AC4" t="n" s="0">
+        <v>45400.0</v>
+      </c>
+      <c r="AD4" t="n" s="0">
+        <v>54300.0</v>
+      </c>
+      <c r="AE4" t="n" s="0">
+        <v>45400.0</v>
+      </c>
+      <c r="AF4" t="n" s="0">
+        <v>45700.0</v>
+      </c>
+      <c r="AG4" t="n" s="0">
+        <v>46700.0</v>
+      </c>
+      <c r="AH4" t="n" s="0">
+        <v>46500.0</v>
+      </c>
+      <c r="AI4" t="n" s="0">
+        <v>53500.0</v>
+      </c>
+      <c r="AJ4" t="n" s="0">
+        <v>54600.0</v>
+      </c>
+      <c r="AK4" t="n" s="0">
+        <v>44700.0</v>
+      </c>
+      <c r="AL4" t="n" s="0">
+        <v>44900.0</v>
+      </c>
+      <c r="AM4" t="n" s="0">
+        <v>90300.0</v>
+      </c>
+      <c r="AN4" t="n" s="0">
+        <v>48200.0</v>
+      </c>
+      <c r="AO4" t="n" s="0">
+        <v>47200.0</v>
+      </c>
+      <c r="AP4" t="n" s="0">
+        <v>45600.0</v>
+      </c>
+      <c r="AQ4" t="n" s="0">
+        <v>44400.0</v>
+      </c>
+      <c r="AR4" t="n" s="0">
+        <v>48400.0</v>
+      </c>
+      <c r="AS4" t="n" s="0">
+        <v>48900.0</v>
+      </c>
+      <c r="AT4" t="n" s="0">
+        <v>45400.0</v>
+      </c>
+      <c r="AU4" t="n" s="0">
+        <v>47800.0</v>
+      </c>
+      <c r="AV4" t="n" s="0">
+        <v>47500.0</v>
+      </c>
+      <c r="AW4" t="n" s="0">
+        <v>46800.0</v>
+      </c>
+      <c r="AX4" t="n" s="0">
+        <v>47000.0</v>
+      </c>
+      <c r="AY4" t="n" s="0">
+        <v>47400.0</v>
+      </c>
+      <c r="AZ4" t="n" s="0">
+        <v>46600.0</v>
+      </c>
+      <c r="BA4" t="n" s="0">
+        <v>46100.0</v>
+      </c>
+      <c r="BB4" t="n" s="0">
+        <v>46300.0</v>
+      </c>
+      <c r="BC4" t="n" s="0">
+        <v>49000.0</v>
+      </c>
+      <c r="BD4" t="n" s="0">
+        <v>48700.0</v>
+      </c>
+      <c r="BE4" t="n" s="0">
+        <v>45600.0</v>
+      </c>
+      <c r="BF4" t="n" s="0">
+        <v>46000.0</v>
+      </c>
+      <c r="BG4" t="n" s="0">
+        <v>46200.0</v>
+      </c>
+      <c r="BH4" t="n" s="0">
+        <v>46900.0</v>
+      </c>
+      <c r="BI4" t="n" s="0">
+        <v>45700.0</v>
+      </c>
+      <c r="BJ4" t="n" s="0">
+        <v>45600.0</v>
+      </c>
+      <c r="BK4" t="n" s="0">
+        <v>46600.0</v>
+      </c>
+      <c r="BL4" t="n" s="0">
+        <v>49900.0</v>
+      </c>
+      <c r="BM4" t="n" s="0">
+        <v>45400.0</v>
+      </c>
+      <c r="BN4" t="n" s="0">
+        <v>45700.0</v>
+      </c>
+      <c r="BO4" t="n" s="0">
+        <v>44600.0</v>
+      </c>
+      <c r="BP4" t="n" s="0">
+        <v>46300.0</v>
+      </c>
+      <c r="BQ4" t="n" s="0">
+        <v>47800.0</v>
+      </c>
+      <c r="BR4" t="n" s="0">
+        <v>54000.0</v>
+      </c>
+      <c r="BS4" t="n" s="0">
+        <v>46100.0</v>
+      </c>
+      <c r="BT4" t="n" s="0">
+        <v>53200.0</v>
+      </c>
+      <c r="BU4" t="n" s="0">
+        <v>54500.0</v>
+      </c>
+      <c r="BV4" t="n" s="0">
+        <v>46400.0</v>
+      </c>
+      <c r="BW4" t="n" s="0">
+        <v>44700.0</v>
+      </c>
+      <c r="BX4" t="n" s="0">
+        <v>46300.0</v>
+      </c>
+      <c r="BY4" t="n" s="0">
+        <v>45700.0</v>
+      </c>
+      <c r="BZ4" t="n" s="0">
+        <v>46600.0</v>
+      </c>
+      <c r="CA4" t="n" s="0">
+        <v>46700.0</v>
+      </c>
+      <c r="CB4" t="n" s="0">
+        <v>46200.0</v>
+      </c>
+      <c r="CC4" t="n" s="0">
+        <v>45300.0</v>
+      </c>
+      <c r="CD4" t="n" s="0">
+        <v>45400.0</v>
+      </c>
+      <c r="CE4" t="n" s="0">
+        <v>64200.0</v>
+      </c>
+      <c r="CF4" t="n" s="0">
+        <v>59800.0</v>
+      </c>
+      <c r="CG4" t="n" s="0">
+        <v>47800.0</v>
+      </c>
+      <c r="CH4" t="n" s="0">
+        <v>47200.0</v>
+      </c>
+      <c r="CI4" t="n" s="0">
+        <v>45000.0</v>
+      </c>
+      <c r="CJ4" t="n" s="0">
+        <v>45400.0</v>
+      </c>
+      <c r="CK4" t="n" s="0">
+        <v>44800.0</v>
+      </c>
+      <c r="CL4" t="n" s="0">
+        <v>46000.0</v>
+      </c>
+      <c r="CM4" t="n" s="0">
+        <v>46400.0</v>
+      </c>
+      <c r="CN4" t="n" s="0">
+        <v>45900.0</v>
+      </c>
+      <c r="CO4" t="n" s="0">
+        <v>45400.0</v>
+      </c>
+      <c r="CP4" t="n" s="0">
+        <v>45100.0</v>
+      </c>
+      <c r="CQ4" t="n" s="0">
+        <v>45000.0</v>
+      </c>
+      <c r="CR4" t="n" s="0">
+        <v>45900.0</v>
+      </c>
+      <c r="CS4" t="n" s="0">
+        <v>49000.0</v>
+      </c>
+      <c r="CT4" t="n" s="0">
+        <v>58500.0</v>
+      </c>
+      <c r="CU4" t="n" s="0">
+        <v>63600.0</v>
+      </c>
+      <c r="CV4" t="n" s="0">
+        <v>47600.0</v>
+      </c>
+      <c r="CW4" t="n" s="0">
+        <v>44600.0</v>
+      </c>
+      <c r="CX4" t="n" s="0">
+        <v>46700.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>1000.0</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>1465200.0</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>3288900.0</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>264000.0</v>
+      </c>
+      <c r="F5" t="n" s="0">
+        <v>96800.0</v>
+      </c>
+      <c r="G5" t="n" s="0">
+        <v>45800.0</v>
+      </c>
+      <c r="H5" t="n" s="0">
+        <v>85000.0</v>
+      </c>
+      <c r="I5" t="n" s="0">
+        <v>45800.0</v>
+      </c>
+      <c r="J5" t="n" s="0">
+        <v>87500.0</v>
+      </c>
+      <c r="K5" t="n" s="0">
+        <v>45400.0</v>
+      </c>
+      <c r="L5" t="n" s="0">
+        <v>44500.0</v>
+      </c>
+      <c r="M5" t="n" s="0">
+        <v>45900.0</v>
+      </c>
+      <c r="N5" t="n" s="0">
+        <v>44300.0</v>
+      </c>
+      <c r="O5" t="n" s="0">
+        <v>47300.0</v>
+      </c>
+      <c r="P5" t="n" s="0">
+        <v>43100.0</v>
+      </c>
+      <c r="Q5" t="n" s="0">
+        <v>48300.0</v>
+      </c>
+      <c r="R5" t="n" s="0">
+        <v>45300.0</v>
+      </c>
+      <c r="S5" t="n" s="0">
+        <v>48800.0</v>
+      </c>
+      <c r="T5" t="n" s="0">
+        <v>98300.0</v>
+      </c>
+      <c r="U5" t="n" s="0">
+        <v>48000.0</v>
+      </c>
+      <c r="V5" t="n" s="0">
+        <v>46800.0</v>
+      </c>
+      <c r="W5" t="n" s="0">
+        <v>54500.0</v>
+      </c>
+      <c r="X5" t="n" s="0">
+        <v>47500.0</v>
+      </c>
+      <c r="Y5" t="n" s="0">
+        <v>45300.0</v>
+      </c>
+      <c r="Z5" t="n" s="0">
+        <v>44600.0</v>
+      </c>
+      <c r="AA5" t="n" s="0">
+        <v>45700.0</v>
+      </c>
+      <c r="AB5" t="n" s="0">
+        <v>125400.0</v>
+      </c>
+      <c r="AC5" t="n" s="0">
+        <v>46000.0</v>
+      </c>
+      <c r="AD5" t="n" s="0">
+        <v>52200.0</v>
+      </c>
+      <c r="AE5" t="n" s="0">
+        <v>45000.0</v>
+      </c>
+      <c r="AF5" t="n" s="0">
+        <v>44600.0</v>
+      </c>
+      <c r="AG5" t="n" s="0">
+        <v>44300.0</v>
+      </c>
+      <c r="AH5" t="n" s="0">
+        <v>48400.0</v>
+      </c>
+      <c r="AI5" t="n" s="0">
+        <v>46500.0</v>
+      </c>
+      <c r="AJ5" t="n" s="0">
+        <v>57400.0</v>
+      </c>
+      <c r="AK5" t="n" s="0">
+        <v>45600.0</v>
+      </c>
+      <c r="AL5" t="n" s="0">
+        <v>46200.0</v>
+      </c>
+      <c r="AM5" t="n" s="0">
+        <v>94300.0</v>
+      </c>
+      <c r="AN5" t="n" s="0">
+        <v>46800.0</v>
+      </c>
+      <c r="AO5" t="n" s="0">
+        <v>45400.0</v>
+      </c>
+      <c r="AP5" t="n" s="0">
+        <v>45900.0</v>
+      </c>
+      <c r="AQ5" t="n" s="0">
+        <v>46200.0</v>
+      </c>
+      <c r="AR5" t="n" s="0">
+        <v>43000.0</v>
+      </c>
+      <c r="AS5" t="n" s="0">
+        <v>44100.0</v>
+      </c>
+      <c r="AT5" t="n" s="0">
+        <v>46600.0</v>
+      </c>
+      <c r="AU5" t="n" s="0">
+        <v>49000.0</v>
+      </c>
+      <c r="AV5" t="n" s="0">
+        <v>44800.0</v>
+      </c>
+      <c r="AW5" t="n" s="0">
+        <v>44700.0</v>
+      </c>
+      <c r="AX5" t="n" s="0">
+        <v>46600.0</v>
+      </c>
+      <c r="AY5" t="n" s="0">
+        <v>45000.0</v>
+      </c>
+      <c r="AZ5" t="n" s="0">
+        <v>45600.0</v>
+      </c>
+      <c r="BA5" t="n" s="0">
+        <v>45500.0</v>
+      </c>
+      <c r="BB5" t="n" s="0">
+        <v>46900.0</v>
+      </c>
+      <c r="BC5" t="n" s="0">
+        <v>47300.0</v>
+      </c>
+      <c r="BD5" t="n" s="0">
+        <v>44400.0</v>
+      </c>
+      <c r="BE5" t="n" s="0">
+        <v>44800.0</v>
+      </c>
+      <c r="BF5" t="n" s="0">
+        <v>44100.0</v>
+      </c>
+      <c r="BG5" t="n" s="0">
+        <v>45600.0</v>
+      </c>
+      <c r="BH5" t="n" s="0">
+        <v>44600.0</v>
+      </c>
+      <c r="BI5" t="n" s="0">
+        <v>45000.0</v>
+      </c>
+      <c r="BJ5" t="n" s="0">
+        <v>44700.0</v>
+      </c>
+      <c r="BK5" t="n" s="0">
+        <v>44400.0</v>
+      </c>
+      <c r="BL5" t="n" s="0">
+        <v>48200.0</v>
+      </c>
+      <c r="BM5" t="n" s="0">
+        <v>45100.0</v>
+      </c>
+      <c r="BN5" t="n" s="0">
+        <v>46100.0</v>
+      </c>
+      <c r="BO5" t="n" s="0">
+        <v>46400.0</v>
+      </c>
+      <c r="BP5" t="n" s="0">
+        <v>44700.0</v>
+      </c>
+      <c r="BQ5" t="n" s="0">
+        <v>43200.0</v>
+      </c>
+      <c r="BR5" t="n" s="0">
+        <v>53200.0</v>
+      </c>
+      <c r="BS5" t="n" s="0">
+        <v>44800.0</v>
+      </c>
+      <c r="BT5" t="n" s="0">
+        <v>52600.0</v>
+      </c>
+      <c r="BU5" t="n" s="0">
+        <v>52900.0</v>
+      </c>
+      <c r="BV5" t="n" s="0">
+        <v>46800.0</v>
+      </c>
+      <c r="BW5" t="n" s="0">
+        <v>48100.0</v>
+      </c>
+      <c r="BX5" t="n" s="0">
+        <v>45100.0</v>
+      </c>
+      <c r="BY5" t="n" s="0">
+        <v>46000.0</v>
+      </c>
+      <c r="BZ5" t="n" s="0">
+        <v>48800.0</v>
+      </c>
+      <c r="CA5" t="n" s="0">
+        <v>43800.0</v>
+      </c>
+      <c r="CB5" t="n" s="0">
+        <v>44200.0</v>
+      </c>
+      <c r="CC5" t="n" s="0">
+        <v>45100.0</v>
+      </c>
+      <c r="CD5" t="n" s="0">
+        <v>44600.0</v>
+      </c>
+      <c r="CE5" t="n" s="0">
+        <v>66700.0</v>
+      </c>
+      <c r="CF5" t="n" s="0">
+        <v>61500.0</v>
+      </c>
+      <c r="CG5" t="n" s="0">
+        <v>47000.0</v>
+      </c>
+      <c r="CH5" t="n" s="0">
+        <v>46100.0</v>
+      </c>
+      <c r="CI5" t="n" s="0">
+        <v>45800.0</v>
+      </c>
+      <c r="CJ5" t="n" s="0">
+        <v>46100.0</v>
+      </c>
+      <c r="CK5" t="n" s="0">
+        <v>47200.0</v>
+      </c>
+      <c r="CL5" t="n" s="0">
+        <v>45900.0</v>
+      </c>
+      <c r="CM5" t="n" s="0">
+        <v>46600.0</v>
+      </c>
+      <c r="CN5" t="n" s="0">
+        <v>45100.0</v>
+      </c>
+      <c r="CO5" t="n" s="0">
+        <v>45600.0</v>
+      </c>
+      <c r="CP5" t="n" s="0">
+        <v>46000.0</v>
+      </c>
+      <c r="CQ5" t="n" s="0">
+        <v>46400.0</v>
+      </c>
+      <c r="CR5" t="n" s="0">
+        <v>46500.0</v>
+      </c>
+      <c r="CS5" t="n" s="0">
+        <v>43300.0</v>
+      </c>
+      <c r="CT5" t="n" s="0">
+        <v>52400.0</v>
+      </c>
+      <c r="CU5" t="n" s="0">
+        <v>71900.0</v>
+      </c>
+      <c r="CV5" t="n" s="0">
+        <v>46600.0</v>
+      </c>
+      <c r="CW5" t="n" s="0">
+        <v>45600.0</v>
+      </c>
+      <c r="CX5" t="n" s="0">
+        <v>44500.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n" s="0">
+        <v>1000.0</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>1591600.0</v>
+      </c>
+      <c r="D6" t="n" s="0">
+        <v>420300.0</v>
+      </c>
+      <c r="E6" t="n" s="0">
+        <v>400400.0</v>
+      </c>
+      <c r="F6" t="n" s="0">
+        <v>448300.0</v>
+      </c>
+      <c r="G6" t="n" s="0">
+        <v>215300.0</v>
+      </c>
+      <c r="H6" t="n" s="0">
+        <v>321600.0</v>
+      </c>
+      <c r="I6" t="n" s="0">
+        <v>223500.0</v>
+      </c>
+      <c r="J6" t="n" s="0">
+        <v>449900.0</v>
+      </c>
+      <c r="K6" t="n" s="0">
+        <v>238200.0</v>
+      </c>
+      <c r="L6" t="n" s="0">
+        <v>209300.0</v>
+      </c>
+      <c r="M6" t="n" s="0">
+        <v>212700.0</v>
+      </c>
+      <c r="N6" t="n" s="0">
+        <v>210400.0</v>
+      </c>
+      <c r="O6" t="n" s="0">
+        <v>210900.0</v>
+      </c>
+      <c r="P6" t="n" s="0">
+        <v>210700.0</v>
+      </c>
+      <c r="Q6" t="n" s="0">
+        <v>210700.0</v>
+      </c>
+      <c r="R6" t="n" s="0">
+        <v>211700.0</v>
+      </c>
+      <c r="S6" t="n" s="0">
+        <v>211900.0</v>
+      </c>
+      <c r="T6" t="n" s="0">
+        <v>441600.0</v>
+      </c>
+      <c r="U6" t="n" s="0">
+        <v>238100.0</v>
+      </c>
+      <c r="V6" t="n" s="0">
+        <v>249200.0</v>
+      </c>
+      <c r="W6" t="n" s="0">
+        <v>217600.0</v>
+      </c>
+      <c r="X6" t="n" s="0">
+        <v>213100.0</v>
+      </c>
+      <c r="Y6" t="n" s="0">
+        <v>216000.0</v>
+      </c>
+      <c r="Z6" t="n" s="0">
+        <v>211200.0</v>
+      </c>
+      <c r="AA6" t="n" s="0">
+        <v>210100.0</v>
+      </c>
+      <c r="AB6" t="n" s="0">
+        <v>480200.0</v>
+      </c>
+      <c r="AC6" t="n" s="0">
+        <v>211500.0</v>
+      </c>
+      <c r="AD6" t="n" s="0">
+        <v>224100.0</v>
+      </c>
+      <c r="AE6" t="n" s="0">
+        <v>213900.0</v>
+      </c>
+      <c r="AF6" t="n" s="0">
+        <v>212000.0</v>
+      </c>
+      <c r="AG6" t="n" s="0">
+        <v>209200.0</v>
+      </c>
+      <c r="AH6" t="n" s="0">
+        <v>211400.0</v>
+      </c>
+      <c r="AI6" t="n" s="0">
+        <v>213000.0</v>
+      </c>
+      <c r="AJ6" t="n" s="0">
+        <v>210100.0</v>
+      </c>
+      <c r="AK6" t="n" s="0">
+        <v>211600.0</v>
+      </c>
+      <c r="AL6" t="n" s="0">
+        <v>211100.0</v>
+      </c>
+      <c r="AM6" t="n" s="0">
+        <v>418500.0</v>
+      </c>
+      <c r="AN6" t="n" s="0">
+        <v>219600.0</v>
+      </c>
+      <c r="AO6" t="n" s="0">
+        <v>429000.0</v>
+      </c>
+      <c r="AP6" t="n" s="0">
+        <v>209000.0</v>
+      </c>
+      <c r="AQ6" t="n" s="0">
+        <v>208000.0</v>
+      </c>
+      <c r="AR6" t="n" s="0">
+        <v>218800.0</v>
+      </c>
+      <c r="AS6" t="n" s="0">
+        <v>211100.0</v>
+      </c>
+      <c r="AT6" t="n" s="0">
+        <v>211400.0</v>
+      </c>
+      <c r="AU6" t="n" s="0">
+        <v>313000.0</v>
+      </c>
+      <c r="AV6" t="n" s="0">
+        <v>220900.0</v>
+      </c>
+      <c r="AW6" t="n" s="0">
+        <v>211400.0</v>
+      </c>
+      <c r="AX6" t="n" s="0">
+        <v>222800.0</v>
+      </c>
+      <c r="AY6" t="n" s="0">
+        <v>229400.0</v>
+      </c>
+      <c r="AZ6" t="n" s="0">
+        <v>212400.0</v>
+      </c>
+      <c r="BA6" t="n" s="0">
+        <v>212700.0</v>
+      </c>
+      <c r="BB6" t="n" s="0">
+        <v>208800.0</v>
+      </c>
+      <c r="BC6" t="n" s="0">
+        <v>220100.0</v>
+      </c>
+      <c r="BD6" t="n" s="0">
+        <v>213300.0</v>
+      </c>
+      <c r="BE6" t="n" s="0">
+        <v>208700.0</v>
+      </c>
+      <c r="BF6" t="n" s="0">
+        <v>210600.0</v>
+      </c>
+      <c r="BG6" t="n" s="0">
+        <v>211400.0</v>
+      </c>
+      <c r="BH6" t="n" s="0">
+        <v>210800.0</v>
+      </c>
+      <c r="BI6" t="n" s="0">
+        <v>210400.0</v>
+      </c>
+      <c r="BJ6" t="n" s="0">
+        <v>210800.0</v>
+      </c>
+      <c r="BK6" t="n" s="0">
+        <v>237400.0</v>
+      </c>
+      <c r="BL6" t="n" s="0">
+        <v>209700.0</v>
+      </c>
+      <c r="BM6" t="n" s="0">
+        <v>211100.0</v>
+      </c>
+      <c r="BN6" t="n" s="0">
+        <v>212700.0</v>
+      </c>
+      <c r="BO6" t="n" s="0">
+        <v>211500.0</v>
+      </c>
+      <c r="BP6" t="n" s="0">
+        <v>210700.0</v>
+      </c>
+      <c r="BQ6" t="n" s="0">
+        <v>211200.0</v>
+      </c>
+      <c r="BR6" t="n" s="0">
+        <v>209700.0</v>
+      </c>
+      <c r="BS6" t="n" s="0">
+        <v>211100.0</v>
+      </c>
+      <c r="BT6" t="n" s="0">
+        <v>227400.0</v>
+      </c>
+      <c r="BU6" t="n" s="0">
+        <v>226200.0</v>
+      </c>
+      <c r="BV6" t="n" s="0">
+        <v>211100.0</v>
+      </c>
+      <c r="BW6" t="n" s="0">
+        <v>209700.0</v>
+      </c>
+      <c r="BX6" t="n" s="0">
+        <v>211700.0</v>
+      </c>
+      <c r="BY6" t="n" s="0">
+        <v>209900.0</v>
+      </c>
+      <c r="BZ6" t="n" s="0">
+        <v>209300.0</v>
+      </c>
+      <c r="CA6" t="n" s="0">
+        <v>211700.0</v>
+      </c>
+      <c r="CB6" t="n" s="0">
+        <v>212800.0</v>
+      </c>
+      <c r="CC6" t="n" s="0">
+        <v>219300.0</v>
+      </c>
+      <c r="CD6" t="n" s="0">
+        <v>212100.0</v>
+      </c>
+      <c r="CE6" t="n" s="0">
+        <v>256100.0</v>
+      </c>
+      <c r="CF6" t="n" s="0">
+        <v>267300.0</v>
+      </c>
+      <c r="CG6" t="n" s="0">
+        <v>223300.0</v>
+      </c>
+      <c r="CH6" t="n" s="0">
+        <v>210600.0</v>
+      </c>
+      <c r="CI6" t="n" s="0">
+        <v>213800.0</v>
+      </c>
+      <c r="CJ6" t="n" s="0">
+        <v>232600.0</v>
+      </c>
+      <c r="CK6" t="n" s="0">
+        <v>209600.0</v>
+      </c>
+      <c r="CL6" t="n" s="0">
+        <v>209900.0</v>
+      </c>
+      <c r="CM6" t="n" s="0">
+        <v>208900.0</v>
+      </c>
+      <c r="CN6" t="n" s="0">
+        <v>210100.0</v>
+      </c>
+      <c r="CO6" t="n" s="0">
+        <v>210700.0</v>
+      </c>
+      <c r="CP6" t="n" s="0">
+        <v>214600.0</v>
+      </c>
+      <c r="CQ6" t="n" s="0">
+        <v>211700.0</v>
+      </c>
+      <c r="CR6" t="n" s="0">
+        <v>211900.0</v>
+      </c>
+      <c r="CS6" t="n" s="0">
+        <v>211200.0</v>
+      </c>
+      <c r="CT6" t="n" s="0">
+        <v>216900.0</v>
+      </c>
+      <c r="CU6" t="n" s="0">
+        <v>225800.0</v>
+      </c>
+      <c r="CV6" t="n" s="0">
+        <v>212300.0</v>
+      </c>
+      <c r="CW6" t="n" s="0">
+        <v>210000.0</v>
+      </c>
+      <c r="CX6" t="n" s="0">
+        <v>215100.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B7" t="n" s="0">
+        <v>1000.0</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>1373300.0</v>
+      </c>
+      <c r="D7" t="n" s="0">
+        <v>1390100.0</v>
+      </c>
+      <c r="E7" t="n" s="0">
+        <v>495000.0</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>442500.0</v>
+      </c>
+      <c r="G7" t="n" s="0">
+        <v>212700.0</v>
+      </c>
+      <c r="H7" t="n" s="0">
+        <v>343800.0</v>
+      </c>
+      <c r="I7" t="n" s="0">
+        <v>212100.0</v>
+      </c>
+      <c r="J7" t="n" s="0">
+        <v>457400.0</v>
+      </c>
+      <c r="K7" t="n" s="0">
+        <v>252200.0</v>
+      </c>
+      <c r="L7" t="n" s="0">
+        <v>211000.0</v>
+      </c>
+      <c r="M7" t="n" s="0">
+        <v>213500.0</v>
+      </c>
+      <c r="N7" t="n" s="0">
+        <v>209900.0</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>211100.0</v>
+      </c>
+      <c r="P7" t="n" s="0">
+        <v>210000.0</v>
+      </c>
+      <c r="Q7" t="n" s="0">
+        <v>212200.0</v>
+      </c>
+      <c r="R7" t="n" s="0">
+        <v>209800.0</v>
+      </c>
+      <c r="S7" t="n" s="0">
+        <v>226200.0</v>
+      </c>
+      <c r="T7" t="n" s="0">
+        <v>446700.0</v>
+      </c>
+      <c r="U7" t="n" s="0">
+        <v>212500.0</v>
+      </c>
+      <c r="V7" t="n" s="0">
+        <v>212700.0</v>
+      </c>
+      <c r="W7" t="n" s="0">
+        <v>210700.0</v>
+      </c>
+      <c r="X7" t="n" s="0">
+        <v>211900.0</v>
+      </c>
+      <c r="Y7" t="n" s="0">
+        <v>263300.0</v>
+      </c>
+      <c r="Z7" t="n" s="0">
+        <v>213200.0</v>
+      </c>
+      <c r="AA7" t="n" s="0">
+        <v>210600.0</v>
+      </c>
+      <c r="AB7" t="n" s="0">
+        <v>445900.0</v>
+      </c>
+      <c r="AC7" t="n" s="0">
+        <v>211900.0</v>
+      </c>
+      <c r="AD7" t="n" s="0">
+        <v>210300.0</v>
+      </c>
+      <c r="AE7" t="n" s="0">
+        <v>211900.0</v>
+      </c>
+      <c r="AF7" t="n" s="0">
+        <v>212800.0</v>
+      </c>
+      <c r="AG7" t="n" s="0">
+        <v>210700.0</v>
+      </c>
+      <c r="AH7" t="n" s="0">
+        <v>211200.0</v>
+      </c>
+      <c r="AI7" t="n" s="0">
+        <v>210500.0</v>
+      </c>
+      <c r="AJ7" t="n" s="0">
+        <v>212200.0</v>
+      </c>
+      <c r="AK7" t="n" s="0">
+        <v>211600.0</v>
+      </c>
+      <c r="AL7" t="n" s="0">
+        <v>211400.0</v>
+      </c>
+      <c r="AM7" t="n" s="0">
+        <v>229800.0</v>
+      </c>
+      <c r="AN7" t="n" s="0">
+        <v>222600.0</v>
+      </c>
+      <c r="AO7" t="n" s="0">
+        <v>328000.0</v>
+      </c>
+      <c r="AP7" t="n" s="0">
+        <v>210900.0</v>
+      </c>
+      <c r="AQ7" t="n" s="0">
+        <v>214600.0</v>
+      </c>
+      <c r="AR7" t="n" s="0">
+        <v>211200.0</v>
+      </c>
+      <c r="AS7" t="n" s="0">
+        <v>210400.0</v>
+      </c>
+      <c r="AT7" t="n" s="0">
+        <v>255500.0</v>
+      </c>
+      <c r="AU7" t="n" s="0">
+        <v>228500.0</v>
+      </c>
+      <c r="AV7" t="n" s="0">
+        <v>251600.0</v>
+      </c>
+      <c r="AW7" t="n" s="0">
+        <v>209500.0</v>
+      </c>
+      <c r="AX7" t="n" s="0">
+        <v>219200.0</v>
+      </c>
+      <c r="AY7" t="n" s="0">
+        <v>248400.0</v>
+      </c>
+      <c r="AZ7" t="n" s="0">
+        <v>210600.0</v>
+      </c>
+      <c r="BA7" t="n" s="0">
+        <v>215500.0</v>
+      </c>
+      <c r="BB7" t="n" s="0">
+        <v>211700.0</v>
+      </c>
+      <c r="BC7" t="n" s="0">
+        <v>220200.0</v>
+      </c>
+      <c r="BD7" t="n" s="0">
+        <v>210500.0</v>
+      </c>
+      <c r="BE7" t="n" s="0">
+        <v>215800.0</v>
+      </c>
+      <c r="BF7" t="n" s="0">
+        <v>213600.0</v>
+      </c>
+      <c r="BG7" t="n" s="0">
+        <v>213700.0</v>
+      </c>
+      <c r="BH7" t="n" s="0">
+        <v>211500.0</v>
+      </c>
+      <c r="BI7" t="n" s="0">
+        <v>209900.0</v>
+      </c>
+      <c r="BJ7" t="n" s="0">
+        <v>212000.0</v>
+      </c>
+      <c r="BK7" t="n" s="0">
+        <v>287300.0</v>
+      </c>
+      <c r="BL7" t="n" s="0">
+        <v>210200.0</v>
+      </c>
+      <c r="BM7" t="n" s="0">
+        <v>274600.0</v>
+      </c>
+      <c r="BN7" t="n" s="0">
+        <v>213100.0</v>
+      </c>
+      <c r="BO7" t="n" s="0">
+        <v>224200.0</v>
+      </c>
+      <c r="BP7" t="n" s="0">
+        <v>213300.0</v>
+      </c>
+      <c r="BQ7" t="n" s="0">
+        <v>211200.0</v>
+      </c>
+      <c r="BR7" t="n" s="0">
+        <v>211800.0</v>
+      </c>
+      <c r="BS7" t="n" s="0">
+        <v>210200.0</v>
+      </c>
+      <c r="BT7" t="n" s="0">
+        <v>218500.0</v>
+      </c>
+      <c r="BU7" t="n" s="0">
+        <v>210800.0</v>
+      </c>
+      <c r="BV7" t="n" s="0">
+        <v>212200.0</v>
+      </c>
+      <c r="BW7" t="n" s="0">
+        <v>209400.0</v>
+      </c>
+      <c r="BX7" t="n" s="0">
+        <v>210500.0</v>
+      </c>
+      <c r="BY7" t="n" s="0">
+        <v>211400.0</v>
+      </c>
+      <c r="BZ7" t="n" s="0">
+        <v>211000.0</v>
+      </c>
+      <c r="CA7" t="n" s="0">
+        <v>209900.0</v>
+      </c>
+      <c r="CB7" t="n" s="0">
+        <v>214200.0</v>
+      </c>
+      <c r="CC7" t="n" s="0">
+        <v>241500.0</v>
+      </c>
+      <c r="CD7" t="n" s="0">
+        <v>211800.0</v>
+      </c>
+      <c r="CE7" t="n" s="0">
+        <v>249500.0</v>
+      </c>
+      <c r="CF7" t="n" s="0">
+        <v>269900.0</v>
+      </c>
+      <c r="CG7" t="n" s="0">
+        <v>223600.0</v>
+      </c>
+      <c r="CH7" t="n" s="0">
+        <v>212900.0</v>
+      </c>
+      <c r="CI7" t="n" s="0">
+        <v>211400.0</v>
+      </c>
+      <c r="CJ7" t="n" s="0">
+        <v>248900.0</v>
+      </c>
+      <c r="CK7" t="n" s="0">
+        <v>210000.0</v>
+      </c>
+      <c r="CL7" t="n" s="0">
+        <v>211600.0</v>
+      </c>
+      <c r="CM7" t="n" s="0">
+        <v>211000.0</v>
+      </c>
+      <c r="CN7" t="n" s="0">
+        <v>210000.0</v>
+      </c>
+      <c r="CO7" t="n" s="0">
+        <v>211900.0</v>
+      </c>
+      <c r="CP7" t="n" s="0">
+        <v>210700.0</v>
+      </c>
+      <c r="CQ7" t="n" s="0">
+        <v>210600.0</v>
+      </c>
+      <c r="CR7" t="n" s="0">
+        <v>211700.0</v>
+      </c>
+      <c r="CS7" t="n" s="0">
+        <v>216700.0</v>
+      </c>
+      <c r="CT7" t="n" s="0">
+        <v>209500.0</v>
+      </c>
+      <c r="CU7" t="n" s="0">
+        <v>212300.0</v>
+      </c>
+      <c r="CV7" t="n" s="0">
+        <v>277000.0</v>
+      </c>
+      <c r="CW7" t="n" s="0">
+        <v>272700.0</v>
+      </c>
+      <c r="CX7" t="n" s="0">
+        <v>209000.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B8" t="n" s="0">
+        <v>1000.0</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>504000.0</v>
+      </c>
+      <c r="D8" t="n" s="0">
+        <v>220600.0</v>
+      </c>
+      <c r="E8" t="n" s="0">
+        <v>158300.0</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>142400.0</v>
+      </c>
+      <c r="G8" t="n" s="0">
+        <v>78300.0</v>
+      </c>
+      <c r="H8" t="n" s="0">
+        <v>134100.0</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>70600.0</v>
+      </c>
+      <c r="J8" t="n" s="0">
+        <v>144300.0</v>
+      </c>
+      <c r="K8" t="n" s="0">
+        <v>68500.0</v>
+      </c>
+      <c r="L8" t="n" s="0">
+        <v>70000.0</v>
+      </c>
+      <c r="M8" t="n" s="0">
+        <v>77200.0</v>
+      </c>
+      <c r="N8" t="n" s="0">
+        <v>70900.0</v>
+      </c>
+      <c r="O8" t="n" s="0">
+        <v>73800.0</v>
+      </c>
+      <c r="P8" t="n" s="0">
+        <v>68300.0</v>
+      </c>
+      <c r="Q8" t="n" s="0">
+        <v>72500.0</v>
+      </c>
+      <c r="R8" t="n" s="0">
+        <v>71700.0</v>
+      </c>
+      <c r="S8" t="n" s="0">
+        <v>74400.0</v>
+      </c>
+      <c r="T8" t="n" s="0">
+        <v>130700.0</v>
+      </c>
+      <c r="U8" t="n" s="0">
+        <v>89800.0</v>
+      </c>
+      <c r="V8" t="n" s="0">
+        <v>86200.0</v>
+      </c>
+      <c r="W8" t="n" s="0">
+        <v>86600.0</v>
+      </c>
+      <c r="X8" t="n" s="0">
+        <v>83400.0</v>
+      </c>
+      <c r="Y8" t="n" s="0">
+        <v>95200.0</v>
+      </c>
+      <c r="Z8" t="n" s="0">
+        <v>85100.0</v>
+      </c>
+      <c r="AA8" t="n" s="0">
+        <v>102200.0</v>
+      </c>
+      <c r="AB8" t="n" s="0">
+        <v>125800.0</v>
+      </c>
+      <c r="AC8" t="n" s="0">
+        <v>68900.0</v>
+      </c>
+      <c r="AD8" t="n" s="0">
+        <v>70600.0</v>
+      </c>
+      <c r="AE8" t="n" s="0">
+        <v>76100.0</v>
+      </c>
+      <c r="AF8" t="n" s="0">
+        <v>76300.0</v>
+      </c>
+      <c r="AG8" t="n" s="0">
+        <v>70500.0</v>
+      </c>
+      <c r="AH8" t="n" s="0">
+        <v>141600.0</v>
+      </c>
+      <c r="AI8" t="n" s="0">
+        <v>68000.0</v>
+      </c>
+      <c r="AJ8" t="n" s="0">
+        <v>70800.0</v>
+      </c>
+      <c r="AK8" t="n" s="0">
+        <v>75900.0</v>
+      </c>
+      <c r="AL8" t="n" s="0">
+        <v>69900.0</v>
+      </c>
+      <c r="AM8" t="n" s="0">
+        <v>70700.0</v>
+      </c>
+      <c r="AN8" t="n" s="0">
+        <v>76600.0</v>
+      </c>
+      <c r="AO8" t="n" s="0">
+        <v>104600.0</v>
+      </c>
+      <c r="AP8" t="n" s="0">
+        <v>69900.0</v>
+      </c>
+      <c r="AQ8" t="n" s="0">
+        <v>72300.0</v>
+      </c>
+      <c r="AR8" t="n" s="0">
+        <v>84400.0</v>
+      </c>
+      <c r="AS8" t="n" s="0">
+        <v>86900.0</v>
+      </c>
+      <c r="AT8" t="n" s="0">
+        <v>89000.0</v>
+      </c>
+      <c r="AU8" t="n" s="0">
+        <v>175700.0</v>
+      </c>
+      <c r="AV8" t="n" s="0">
+        <v>73200.0</v>
+      </c>
+      <c r="AW8" t="n" s="0">
+        <v>68500.0</v>
+      </c>
+      <c r="AX8" t="n" s="0">
+        <v>76700.0</v>
+      </c>
+      <c r="AY8" t="n" s="0">
+        <v>72500.0</v>
+      </c>
+      <c r="AZ8" t="n" s="0">
+        <v>69000.0</v>
+      </c>
+      <c r="BA8" t="n" s="0">
+        <v>102400.0</v>
+      </c>
+      <c r="BB8" t="n" s="0">
+        <v>86600.0</v>
+      </c>
+      <c r="BC8" t="n" s="0">
+        <v>88400.0</v>
+      </c>
+      <c r="BD8" t="n" s="0">
+        <v>84900.0</v>
+      </c>
+      <c r="BE8" t="n" s="0">
+        <v>90600.0</v>
+      </c>
+      <c r="BF8" t="n" s="0">
+        <v>85100.0</v>
+      </c>
+      <c r="BG8" t="n" s="0">
+        <v>83300.0</v>
+      </c>
+      <c r="BH8" t="n" s="0">
+        <v>83200.0</v>
+      </c>
+      <c r="BI8" t="n" s="0">
+        <v>87400.0</v>
+      </c>
+      <c r="BJ8" t="n" s="0">
+        <v>83800.0</v>
+      </c>
+      <c r="BK8" t="n" s="0">
+        <v>120400.0</v>
+      </c>
+      <c r="BL8" t="n" s="0">
+        <v>85400.0</v>
+      </c>
+      <c r="BM8" t="n" s="0">
+        <v>88100.0</v>
+      </c>
+      <c r="BN8" t="n" s="0">
+        <v>83300.0</v>
+      </c>
+      <c r="BO8" t="n" s="0">
+        <v>100500.0</v>
+      </c>
+      <c r="BP8" t="n" s="0">
+        <v>82100.0</v>
+      </c>
+      <c r="BQ8" t="n" s="0">
+        <v>90700.0</v>
+      </c>
+      <c r="BR8" t="n" s="0">
+        <v>83400.0</v>
+      </c>
+      <c r="BS8" t="n" s="0">
+        <v>98600.0</v>
+      </c>
+      <c r="BT8" t="n" s="0">
+        <v>94500.0</v>
+      </c>
+      <c r="BU8" t="n" s="0">
+        <v>109200.0</v>
+      </c>
+      <c r="BV8" t="n" s="0">
+        <v>84300.0</v>
+      </c>
+      <c r="BW8" t="n" s="0">
+        <v>84700.0</v>
+      </c>
+      <c r="BX8" t="n" s="0">
+        <v>83500.0</v>
+      </c>
+      <c r="BY8" t="n" s="0">
+        <v>94100.0</v>
+      </c>
+      <c r="BZ8" t="n" s="0">
+        <v>90200.0</v>
+      </c>
+      <c r="CA8" t="n" s="0">
+        <v>87000.0</v>
+      </c>
+      <c r="CB8" t="n" s="0">
+        <v>83300.0</v>
+      </c>
+      <c r="CC8" t="n" s="0">
+        <v>96600.0</v>
+      </c>
+      <c r="CD8" t="n" s="0">
+        <v>82400.0</v>
+      </c>
+      <c r="CE8" t="n" s="0">
+        <v>122000.0</v>
+      </c>
+      <c r="CF8" t="n" s="0">
+        <v>110400.0</v>
+      </c>
+      <c r="CG8" t="n" s="0">
+        <v>111200.0</v>
+      </c>
+      <c r="CH8" t="n" s="0">
+        <v>69500.0</v>
+      </c>
+      <c r="CI8" t="n" s="0">
+        <v>69600.0</v>
+      </c>
+      <c r="CJ8" t="n" s="0">
+        <v>76900.0</v>
+      </c>
+      <c r="CK8" t="n" s="0">
+        <v>79200.0</v>
+      </c>
+      <c r="CL8" t="n" s="0">
+        <v>68800.0</v>
+      </c>
+      <c r="CM8" t="n" s="0">
+        <v>69600.0</v>
+      </c>
+      <c r="CN8" t="n" s="0">
+        <v>72400.0</v>
+      </c>
+      <c r="CO8" t="n" s="0">
+        <v>71100.0</v>
+      </c>
+      <c r="CP8" t="n" s="0">
+        <v>81300.0</v>
+      </c>
+      <c r="CQ8" t="n" s="0">
+        <v>70600.0</v>
+      </c>
+      <c r="CR8" t="n" s="0">
+        <v>70900.0</v>
+      </c>
+      <c r="CS8" t="n" s="0">
+        <v>68600.0</v>
+      </c>
+      <c r="CT8" t="n" s="0">
+        <v>71600.0</v>
+      </c>
+      <c r="CU8" t="n" s="0">
+        <v>78900.0</v>
+      </c>
+      <c r="CV8" t="n" s="0">
+        <v>71600.0</v>
+      </c>
+      <c r="CW8" t="n" s="0">
+        <v>78800.0</v>
+      </c>
+      <c r="CX8" t="n" s="0">
+        <v>69500.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B9" t="n" s="0">
+        <v>1000.0</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>479100.0</v>
+      </c>
+      <c r="D9" t="n" s="0">
+        <v>117500.0</v>
+      </c>
+      <c r="E9" t="n" s="0">
+        <v>147900.0</v>
+      </c>
+      <c r="F9" t="n" s="0">
+        <v>132900.0</v>
+      </c>
+      <c r="G9" t="n" s="0">
+        <v>85000.0</v>
+      </c>
+      <c r="H9" t="n" s="0">
+        <v>118500.0</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>71800.0</v>
+      </c>
+      <c r="J9" t="n" s="0">
+        <v>156100.0</v>
+      </c>
+      <c r="K9" t="n" s="0">
+        <v>75600.0</v>
+      </c>
+      <c r="L9" t="n" s="0">
+        <v>74900.0</v>
+      </c>
+      <c r="M9" t="n" s="0">
+        <v>70100.0</v>
+      </c>
+      <c r="N9" t="n" s="0">
+        <v>70900.0</v>
+      </c>
+      <c r="O9" t="n" s="0">
+        <v>72800.0</v>
+      </c>
+      <c r="P9" t="n" s="0">
+        <v>7206800.0</v>
+      </c>
+      <c r="Q9" t="n" s="0">
+        <v>70200.0</v>
+      </c>
+      <c r="R9" t="n" s="0">
+        <v>74500.0</v>
+      </c>
+      <c r="S9" t="n" s="0">
+        <v>75800.0</v>
+      </c>
+      <c r="T9" t="n" s="0">
+        <v>128100.0</v>
+      </c>
+      <c r="U9" t="n" s="0">
+        <v>84000.0</v>
+      </c>
+      <c r="V9" t="n" s="0">
+        <v>116400.0</v>
+      </c>
+      <c r="W9" t="n" s="0">
+        <v>83200.0</v>
+      </c>
+      <c r="X9" t="n" s="0">
+        <v>83200.0</v>
+      </c>
+      <c r="Y9" t="n" s="0">
+        <v>87700.0</v>
+      </c>
+      <c r="Z9" t="n" s="0">
+        <v>101200.0</v>
+      </c>
+      <c r="AA9" t="n" s="0">
+        <v>88700.0</v>
+      </c>
+      <c r="AB9" t="n" s="0">
+        <v>127900.0</v>
+      </c>
+      <c r="AC9" t="n" s="0">
+        <v>69700.0</v>
+      </c>
+      <c r="AD9" t="n" s="0">
+        <v>71100.0</v>
+      </c>
+      <c r="AE9" t="n" s="0">
+        <v>80600.0</v>
+      </c>
+      <c r="AF9" t="n" s="0">
+        <v>72900.0</v>
+      </c>
+      <c r="AG9" t="n" s="0">
+        <v>69900.0</v>
+      </c>
+      <c r="AH9" t="n" s="0">
+        <v>77700.0</v>
+      </c>
+      <c r="AI9" t="n" s="0">
+        <v>71300.0</v>
+      </c>
+      <c r="AJ9" t="n" s="0">
+        <v>74400.0</v>
+      </c>
+      <c r="AK9" t="n" s="0">
+        <v>70600.0</v>
+      </c>
+      <c r="AL9" t="n" s="0">
+        <v>160400.0</v>
+      </c>
+      <c r="AM9" t="n" s="0">
+        <v>76200.0</v>
+      </c>
+      <c r="AN9" t="n" s="0">
+        <v>72500.0</v>
+      </c>
+      <c r="AO9" t="n" s="0">
+        <v>98200.0</v>
+      </c>
+      <c r="AP9" t="n" s="0">
+        <v>73500.0</v>
+      </c>
+      <c r="AQ9" t="n" s="0">
+        <v>73600.0</v>
+      </c>
+      <c r="AR9" t="n" s="0">
+        <v>83400.0</v>
+      </c>
+      <c r="AS9" t="n" s="0">
+        <v>81200.0</v>
+      </c>
+      <c r="AT9" t="n" s="0">
+        <v>81000.0</v>
+      </c>
+      <c r="AU9" t="n" s="0">
+        <v>101600.0</v>
+      </c>
+      <c r="AV9" t="n" s="0">
+        <v>73600.0</v>
+      </c>
+      <c r="AW9" t="n" s="0">
+        <v>72300.0</v>
+      </c>
+      <c r="AX9" t="n" s="0">
+        <v>73100.0</v>
+      </c>
+      <c r="AY9" t="n" s="0">
+        <v>73200.0</v>
+      </c>
+      <c r="AZ9" t="n" s="0">
+        <v>77300.0</v>
+      </c>
+      <c r="BA9" t="n" s="0">
+        <v>83100.0</v>
+      </c>
+      <c r="BB9" t="n" s="0">
+        <v>86000.0</v>
+      </c>
+      <c r="BC9" t="n" s="0">
+        <v>84400.0</v>
+      </c>
+      <c r="BD9" t="n" s="0">
+        <v>139200.0</v>
+      </c>
+      <c r="BE9" t="n" s="0">
+        <v>81500.0</v>
+      </c>
+      <c r="BF9" t="n" s="0">
+        <v>85600.0</v>
+      </c>
+      <c r="BG9" t="n" s="0">
+        <v>81900.0</v>
+      </c>
+      <c r="BH9" t="n" s="0">
+        <v>85600.0</v>
+      </c>
+      <c r="BI9" t="n" s="0">
+        <v>82200.0</v>
+      </c>
+      <c r="BJ9" t="n" s="0">
+        <v>113800.0</v>
+      </c>
+      <c r="BK9" t="n" s="0">
+        <v>85100.0</v>
+      </c>
+      <c r="BL9" t="n" s="0">
+        <v>84700.0</v>
+      </c>
+      <c r="BM9" t="n" s="0">
+        <v>82200.0</v>
+      </c>
+      <c r="BN9" t="n" s="0">
+        <v>86100.0</v>
+      </c>
+      <c r="BO9" t="n" s="0">
+        <v>86600.0</v>
+      </c>
+      <c r="BP9" t="n" s="0">
+        <v>82700.0</v>
+      </c>
+      <c r="BQ9" t="n" s="0">
+        <v>83600.0</v>
+      </c>
+      <c r="BR9" t="n" s="0">
+        <v>82500.0</v>
+      </c>
+      <c r="BS9" t="n" s="0">
+        <v>82300.0</v>
+      </c>
+      <c r="BT9" t="n" s="0">
+        <v>94500.0</v>
+      </c>
+      <c r="BU9" t="n" s="0">
+        <v>82100.0</v>
+      </c>
+      <c r="BV9" t="n" s="0">
+        <v>85800.0</v>
+      </c>
+      <c r="BW9" t="n" s="0">
+        <v>84500.0</v>
+      </c>
+      <c r="BX9" t="n" s="0">
+        <v>83200.0</v>
+      </c>
+      <c r="BY9" t="n" s="0">
+        <v>81800.0</v>
+      </c>
+      <c r="BZ9" t="n" s="0">
+        <v>87400.0</v>
+      </c>
+      <c r="CA9" t="n" s="0">
+        <v>80100.0</v>
+      </c>
+      <c r="CB9" t="n" s="0">
+        <v>83700.0</v>
+      </c>
+      <c r="CC9" t="n" s="0">
+        <v>86500.0</v>
+      </c>
+      <c r="CD9" t="n" s="0">
+        <v>81800.0</v>
+      </c>
+      <c r="CE9" t="n" s="0">
+        <v>96900.0</v>
+      </c>
+      <c r="CF9" t="n" s="0">
+        <v>108700.0</v>
+      </c>
+      <c r="CG9" t="n" s="0">
+        <v>181500.0</v>
+      </c>
+      <c r="CH9" t="n" s="0">
+        <v>72600.0</v>
+      </c>
+      <c r="CI9" t="n" s="0">
+        <v>69200.0</v>
+      </c>
+      <c r="CJ9" t="n" s="0">
+        <v>82800.0</v>
+      </c>
+      <c r="CK9" t="n" s="0">
+        <v>69500.0</v>
+      </c>
+      <c r="CL9" t="n" s="0">
+        <v>71300.0</v>
+      </c>
+      <c r="CM9" t="n" s="0">
+        <v>70900.0</v>
+      </c>
+      <c r="CN9" t="n" s="0">
+        <v>69100.0</v>
+      </c>
+      <c r="CO9" t="n" s="0">
+        <v>82200.0</v>
+      </c>
+      <c r="CP9" t="n" s="0">
+        <v>72700.0</v>
+      </c>
+      <c r="CQ9" t="n" s="0">
+        <v>77300.0</v>
+      </c>
+      <c r="CR9" t="n" s="0">
+        <v>69300.0</v>
+      </c>
+      <c r="CS9" t="n" s="0">
+        <v>70200.0</v>
+      </c>
+      <c r="CT9" t="n" s="0">
+        <v>69800.0</v>
+      </c>
+      <c r="CU9" t="n" s="0">
+        <v>73300.0</v>
+      </c>
+      <c r="CV9" t="n" s="0">
+        <v>91300.0</v>
+      </c>
+      <c r="CW9" t="n" s="0">
+        <v>76000.0</v>
+      </c>
+      <c r="CX9" t="n" s="0">
+        <v>71800.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B10" t="n" s="0">
+        <v>1000.0</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>563000.0</v>
+      </c>
+      <c r="D10" t="n" s="0">
+        <v>136500.0</v>
+      </c>
+      <c r="E10" t="n" s="0">
+        <v>156400.0</v>
+      </c>
+      <c r="F10" t="n" s="0">
+        <v>206400.0</v>
+      </c>
+      <c r="G10" t="n" s="0">
+        <v>120100.0</v>
+      </c>
+      <c r="H10" t="n" s="0">
+        <v>249000.0</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>117700.0</v>
+      </c>
+      <c r="J10" t="n" s="0">
+        <v>152500.0</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>98500.0</v>
+      </c>
+      <c r="L10" t="n" s="0">
+        <v>97000.0</v>
+      </c>
+      <c r="M10" t="n" s="0">
+        <v>102200.0</v>
+      </c>
+      <c r="N10" t="n" s="0">
+        <v>95100.0</v>
+      </c>
+      <c r="O10" t="n" s="0">
+        <v>103500.0</v>
+      </c>
+      <c r="P10" t="n" s="0">
+        <v>109800.0</v>
+      </c>
+      <c r="Q10" t="n" s="0">
+        <v>98900.0</v>
+      </c>
+      <c r="R10" t="n" s="0">
+        <v>94300.0</v>
+      </c>
+      <c r="S10" t="n" s="0">
+        <v>100800.0</v>
+      </c>
+      <c r="T10" t="n" s="0">
+        <v>140900.0</v>
+      </c>
+      <c r="U10" t="n" s="0">
+        <v>200800.0</v>
+      </c>
+      <c r="V10" t="n" s="0">
+        <v>110600.0</v>
+      </c>
+      <c r="W10" t="n" s="0">
+        <v>113500.0</v>
+      </c>
+      <c r="X10" t="n" s="0">
+        <v>110900.0</v>
+      </c>
+      <c r="Y10" t="n" s="0">
+        <v>143400.0</v>
+      </c>
+      <c r="Z10" t="n" s="0">
+        <v>117700.0</v>
+      </c>
+      <c r="AA10" t="n" s="0">
+        <v>125600.0</v>
+      </c>
+      <c r="AB10" t="n" s="0">
+        <v>142400.0</v>
+      </c>
+      <c r="AC10" t="n" s="0">
+        <v>99700.0</v>
+      </c>
+      <c r="AD10" t="n" s="0">
+        <v>104800.0</v>
+      </c>
+      <c r="AE10" t="n" s="0">
+        <v>95800.0</v>
+      </c>
+      <c r="AF10" t="n" s="0">
+        <v>94500.0</v>
+      </c>
+      <c r="AG10" t="n" s="0">
+        <v>95300.0</v>
+      </c>
+      <c r="AH10" t="n" s="0">
+        <v>99700.0</v>
+      </c>
+      <c r="AI10" t="n" s="0">
+        <v>109500.0</v>
+      </c>
+      <c r="AJ10" t="n" s="0">
+        <v>93400.0</v>
+      </c>
+      <c r="AK10" t="n" s="0">
+        <v>93600.0</v>
+      </c>
+      <c r="AL10" t="n" s="0">
+        <v>112800.0</v>
+      </c>
+      <c r="AM10" t="n" s="0">
+        <v>97200.0</v>
+      </c>
+      <c r="AN10" t="n" s="0">
+        <v>94900.0</v>
+      </c>
+      <c r="AO10" t="n" s="0">
+        <v>126900.0</v>
+      </c>
+      <c r="AP10" t="n" s="0">
+        <v>95900.0</v>
+      </c>
+      <c r="AQ10" t="n" s="0">
+        <v>92800.0</v>
+      </c>
+      <c r="AR10" t="n" s="0">
+        <v>136200.0</v>
+      </c>
+      <c r="AS10" t="n" s="0">
+        <v>113300.0</v>
+      </c>
+      <c r="AT10" t="n" s="0">
+        <v>111600.0</v>
+      </c>
+      <c r="AU10" t="n" s="0">
+        <v>121600.0</v>
+      </c>
+      <c r="AV10" t="n" s="0">
+        <v>102300.0</v>
+      </c>
+      <c r="AW10" t="n" s="0">
+        <v>95500.0</v>
+      </c>
+      <c r="AX10" t="n" s="0">
+        <v>97600.0</v>
+      </c>
+      <c r="AY10" t="n" s="0">
+        <v>106700.0</v>
+      </c>
+      <c r="AZ10" t="n" s="0">
+        <v>97100.0</v>
+      </c>
+      <c r="BA10" t="n" s="0">
+        <v>116900.0</v>
+      </c>
+      <c r="BB10" t="n" s="0">
+        <v>108900.0</v>
+      </c>
+      <c r="BC10" t="n" s="0">
+        <v>120200.0</v>
+      </c>
+      <c r="BD10" t="n" s="0">
+        <v>160300.0</v>
+      </c>
+      <c r="BE10" t="n" s="0">
+        <v>116100.0</v>
+      </c>
+      <c r="BF10" t="n" s="0">
+        <v>108000.0</v>
+      </c>
+      <c r="BG10" t="n" s="0">
+        <v>111600.0</v>
+      </c>
+      <c r="BH10" t="n" s="0">
+        <v>109200.0</v>
+      </c>
+      <c r="BI10" t="n" s="0">
+        <v>137100.0</v>
+      </c>
+      <c r="BJ10" t="n" s="0">
+        <v>110700.0</v>
+      </c>
+      <c r="BK10" t="n" s="0">
+        <v>116900.0</v>
+      </c>
+      <c r="BL10" t="n" s="0">
+        <v>111900.0</v>
+      </c>
+      <c r="BM10" t="n" s="0">
+        <v>112000.0</v>
+      </c>
+      <c r="BN10" t="n" s="0">
+        <v>110800.0</v>
+      </c>
+      <c r="BO10" t="n" s="0">
+        <v>121100.0</v>
+      </c>
+      <c r="BP10" t="n" s="0">
+        <v>114700.0</v>
+      </c>
+      <c r="BQ10" t="n" s="0">
+        <v>109400.0</v>
+      </c>
+      <c r="BR10" t="n" s="0">
+        <v>113400.0</v>
+      </c>
+      <c r="BS10" t="n" s="0">
+        <v>113900.0</v>
+      </c>
+      <c r="BT10" t="n" s="0">
+        <v>138100.0</v>
+      </c>
+      <c r="BU10" t="n" s="0">
+        <v>114200.0</v>
+      </c>
+      <c r="BV10" t="n" s="0">
+        <v>111700.0</v>
+      </c>
+      <c r="BW10" t="n" s="0">
+        <v>108600.0</v>
+      </c>
+      <c r="BX10" t="n" s="0">
+        <v>108700.0</v>
+      </c>
+      <c r="BY10" t="n" s="0">
+        <v>112400.0</v>
+      </c>
+      <c r="BZ10" t="n" s="0">
+        <v>112800.0</v>
+      </c>
+      <c r="CA10" t="n" s="0">
+        <v>108100.0</v>
+      </c>
+      <c r="CB10" t="n" s="0">
+        <v>116900.0</v>
+      </c>
+      <c r="CC10" t="n" s="0">
+        <v>115500.0</v>
+      </c>
+      <c r="CD10" t="n" s="0">
+        <v>138100.0</v>
+      </c>
+      <c r="CE10" t="n" s="0">
+        <v>125600.0</v>
+      </c>
+      <c r="CF10" t="n" s="0">
+        <v>149300.0</v>
+      </c>
+      <c r="CG10" t="n" s="0">
+        <v>124900.0</v>
+      </c>
+      <c r="CH10" t="n" s="0">
+        <v>94000.0</v>
+      </c>
+      <c r="CI10" t="n" s="0">
+        <v>99000.0</v>
+      </c>
+      <c r="CJ10" t="n" s="0">
+        <v>95500.0</v>
+      </c>
+      <c r="CK10" t="n" s="0">
+        <v>95000.0</v>
+      </c>
+      <c r="CL10" t="n" s="0">
+        <v>96500.0</v>
+      </c>
+      <c r="CM10" t="n" s="0">
+        <v>102300.0</v>
+      </c>
+      <c r="CN10" t="n" s="0">
+        <v>101400.0</v>
+      </c>
+      <c r="CO10" t="n" s="0">
+        <v>95500.0</v>
+      </c>
+      <c r="CP10" t="n" s="0">
+        <v>95500.0</v>
+      </c>
+      <c r="CQ10" t="n" s="0">
+        <v>97500.0</v>
+      </c>
+      <c r="CR10" t="n" s="0">
+        <v>94600.0</v>
+      </c>
+      <c r="CS10" t="n" s="0">
+        <v>93400.0</v>
+      </c>
+      <c r="CT10" t="n" s="0">
+        <v>103800.0</v>
+      </c>
+      <c r="CU10" t="n" s="0">
+        <v>106500.0</v>
+      </c>
+      <c r="CV10" t="n" s="0">
+        <v>110800.0</v>
+      </c>
+      <c r="CW10" t="n" s="0">
+        <v>92100.0</v>
+      </c>
+      <c r="CX10" t="n" s="0">
+        <v>89300.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B11" t="n" s="0">
+        <v>1000.0</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>461100.0</v>
+      </c>
+      <c r="D11" t="n" s="0">
+        <v>111200.0</v>
+      </c>
+      <c r="E11" t="n" s="0">
+        <v>150200.0</v>
+      </c>
+      <c r="F11" t="n" s="0">
+        <v>196900.0</v>
+      </c>
+      <c r="G11" t="n" s="0">
+        <v>126500.0</v>
+      </c>
+      <c r="H11" t="n" s="0">
+        <v>184900.0</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>109300.0</v>
+      </c>
+      <c r="J11" t="n" s="0">
+        <v>163500.0</v>
+      </c>
+      <c r="K11" t="n" s="0">
+        <v>99200.0</v>
+      </c>
+      <c r="L11" t="n" s="0">
+        <v>98300.0</v>
+      </c>
+      <c r="M11" t="n" s="0">
+        <v>98100.0</v>
+      </c>
+      <c r="N11" t="n" s="0">
+        <v>100500.0</v>
+      </c>
+      <c r="O11" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+      <c r="P11" t="n" s="0">
+        <v>110900.0</v>
+      </c>
+      <c r="Q11" t="n" s="0">
+        <v>98200.0</v>
+      </c>
+      <c r="R11" t="n" s="0">
+        <v>95200.0</v>
+      </c>
+      <c r="S11" t="n" s="0">
+        <v>92400.0</v>
+      </c>
+      <c r="T11" t="n" s="0">
+        <v>140100.0</v>
+      </c>
+      <c r="U11" t="n" s="0">
+        <v>117800.0</v>
+      </c>
+      <c r="V11" t="n" s="0">
+        <v>107500.0</v>
+      </c>
+      <c r="W11" t="n" s="0">
+        <v>112200.0</v>
+      </c>
+      <c r="X11" t="n" s="0">
+        <v>130000.0</v>
+      </c>
+      <c r="Y11" t="n" s="0">
+        <v>225400.0</v>
+      </c>
+      <c r="Z11" t="n" s="0">
+        <v>109600.0</v>
+      </c>
+      <c r="AA11" t="n" s="0">
+        <v>120500.0</v>
+      </c>
+      <c r="AB11" t="n" s="0">
+        <v>141700.0</v>
+      </c>
+      <c r="AC11" t="n" s="0">
+        <v>95000.0</v>
+      </c>
+      <c r="AD11" t="n" s="0">
+        <v>95900.0</v>
+      </c>
+      <c r="AE11" t="n" s="0">
+        <v>96100.0</v>
+      </c>
+      <c r="AF11" t="n" s="0">
+        <v>97200.0</v>
+      </c>
+      <c r="AG11" t="n" s="0">
+        <v>102700.0</v>
+      </c>
+      <c r="AH11" t="n" s="0">
+        <v>99100.0</v>
+      </c>
+      <c r="AI11" t="n" s="0">
+        <v>95000.0</v>
+      </c>
+      <c r="AJ11" t="n" s="0">
+        <v>90900.0</v>
+      </c>
+      <c r="AK11" t="n" s="0">
+        <v>95100.0</v>
+      </c>
+      <c r="AL11" t="n" s="0">
+        <v>110400.0</v>
+      </c>
+      <c r="AM11" t="n" s="0">
+        <v>97500.0</v>
+      </c>
+      <c r="AN11" t="n" s="0">
+        <v>116000.0</v>
+      </c>
+      <c r="AO11" t="n" s="0">
+        <v>110300.0</v>
+      </c>
+      <c r="AP11" t="n" s="0">
+        <v>98300.0</v>
+      </c>
+      <c r="AQ11" t="n" s="0">
+        <v>97800.0</v>
+      </c>
+      <c r="AR11" t="n" s="0">
+        <v>142100.0</v>
+      </c>
+      <c r="AS11" t="n" s="0">
+        <v>112500.0</v>
+      </c>
+      <c r="AT11" t="n" s="0">
+        <v>111100.0</v>
+      </c>
+      <c r="AU11" t="n" s="0">
+        <v>129100.0</v>
+      </c>
+      <c r="AV11" t="n" s="0">
+        <v>106900.0</v>
+      </c>
+      <c r="AW11" t="n" s="0">
+        <v>97400.0</v>
+      </c>
+      <c r="AX11" t="n" s="0">
+        <v>104600.0</v>
+      </c>
+      <c r="AY11" t="n" s="0">
+        <v>97600.0</v>
+      </c>
+      <c r="AZ11" t="n" s="0">
+        <v>92700.0</v>
+      </c>
+      <c r="BA11" t="n" s="0">
+        <v>115700.0</v>
+      </c>
+      <c r="BB11" t="n" s="0">
+        <v>111200.0</v>
+      </c>
+      <c r="BC11" t="n" s="0">
+        <v>2160400.0</v>
+      </c>
+      <c r="BD11" t="n" s="0">
+        <v>129800.0</v>
+      </c>
+      <c r="BE11" t="n" s="0">
+        <v>113500.0</v>
+      </c>
+      <c r="BF11" t="n" s="0">
+        <v>110000.0</v>
+      </c>
+      <c r="BG11" t="n" s="0">
+        <v>111600.0</v>
+      </c>
+      <c r="BH11" t="n" s="0">
+        <v>127600.0</v>
+      </c>
+      <c r="BI11" t="n" s="0">
+        <v>115400.0</v>
+      </c>
+      <c r="BJ11" t="n" s="0">
+        <v>107300.0</v>
+      </c>
+      <c r="BK11" t="n" s="0">
+        <v>114300.0</v>
+      </c>
+      <c r="BL11" t="n" s="0">
+        <v>109300.0</v>
+      </c>
+      <c r="BM11" t="n" s="0">
+        <v>112700.0</v>
+      </c>
+      <c r="BN11" t="n" s="0">
+        <v>112100.0</v>
+      </c>
+      <c r="BO11" t="n" s="0">
+        <v>123900.0</v>
+      </c>
+      <c r="BP11" t="n" s="0">
+        <v>117200.0</v>
+      </c>
+      <c r="BQ11" t="n" s="0">
+        <v>114400.0</v>
+      </c>
+      <c r="BR11" t="n" s="0">
+        <v>113800.0</v>
+      </c>
+      <c r="BS11" t="n" s="0">
+        <v>129100.0</v>
+      </c>
+      <c r="BT11" t="n" s="0">
+        <v>115300.0</v>
+      </c>
+      <c r="BU11" t="n" s="0">
+        <v>114600.0</v>
+      </c>
+      <c r="BV11" t="n" s="0">
+        <v>110800.0</v>
+      </c>
+      <c r="BW11" t="n" s="0">
+        <v>108400.0</v>
+      </c>
+      <c r="BX11" t="n" s="0">
+        <v>112400.0</v>
+      </c>
+      <c r="BY11" t="n" s="0">
+        <v>116400.0</v>
+      </c>
+      <c r="BZ11" t="n" s="0">
+        <v>160000.0</v>
+      </c>
+      <c r="CA11" t="n" s="0">
+        <v>112500.0</v>
+      </c>
+      <c r="CB11" t="n" s="0">
+        <v>114500.0</v>
+      </c>
+      <c r="CC11" t="n" s="0">
+        <v>126300.0</v>
+      </c>
+      <c r="CD11" t="n" s="0">
+        <v>117000.0</v>
+      </c>
+      <c r="CE11" t="n" s="0">
+        <v>130600.0</v>
+      </c>
+      <c r="CF11" t="n" s="0">
+        <v>143200.0</v>
+      </c>
+      <c r="CG11" t="n" s="0">
+        <v>121900.0</v>
+      </c>
+      <c r="CH11" t="n" s="0">
+        <v>98500.0</v>
+      </c>
+      <c r="CI11" t="n" s="0">
+        <v>96100.0</v>
+      </c>
+      <c r="CJ11" t="n" s="0">
+        <v>96600.0</v>
+      </c>
+      <c r="CK11" t="n" s="0">
+        <v>96700.0</v>
+      </c>
+      <c r="CL11" t="n" s="0">
+        <v>90300.0</v>
+      </c>
+      <c r="CM11" t="n" s="0">
+        <v>162000.0</v>
+      </c>
+      <c r="CN11" t="n" s="0">
+        <v>97100.0</v>
+      </c>
+      <c r="CO11" t="n" s="0">
+        <v>98500.0</v>
+      </c>
+      <c r="CP11" t="n" s="0">
+        <v>90100.0</v>
+      </c>
+      <c r="CQ11" t="n" s="0">
+        <v>96600.0</v>
+      </c>
+      <c r="CR11" t="n" s="0">
+        <v>97000.0</v>
+      </c>
+      <c r="CS11" t="n" s="0">
+        <v>103600.0</v>
+      </c>
+      <c r="CT11" t="n" s="0">
+        <v>96700.0</v>
+      </c>
+      <c r="CU11" t="n" s="0">
+        <v>94500.0</v>
+      </c>
+      <c r="CV11" t="n" s="0">
+        <v>113200.0</v>
+      </c>
+      <c r="CW11" t="n" s="0">
+        <v>93300.0</v>
+      </c>
+      <c r="CX11" t="n" s="0">
+        <v>101200.0</v>
       </c>
     </row>
   </sheetData>

--- a/excel/1000(n)/RAW_Dataset.xlsx
+++ b/excel/1000(n)/RAW_Dataset.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="31">
   <si>
     <t xml:space="preserve">Algorithm </t>
   </si>
@@ -234,64 +234,64 @@
         <v>1000.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>2826700.0</v>
+        <v>1047900.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>1128600.0</v>
+        <v>1193000.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>996100.0</v>
+        <v>1061600.0</v>
       </c>
       <c r="G2" t="n" s="0">
-        <v>1161900.0</v>
+        <v>850300.0</v>
       </c>
       <c r="H2" t="n" s="0">
-        <v>1095500.0</v>
+        <v>1127100.0</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>1151900.0</v>
+        <v>571200.0</v>
       </c>
       <c r="J2" t="n" s="0">
-        <v>735400.0</v>
+        <v>1171200.0</v>
       </c>
       <c r="K2" t="n" s="0">
-        <v>904200.0</v>
+        <v>589600.0</v>
       </c>
       <c r="L2" t="n" s="0">
+        <v>770700.0</v>
+      </c>
+      <c r="M2" t="n" s="0">
+        <v>1141400.0</v>
+      </c>
+      <c r="N2" t="n" s="0">
+        <v>566600.0</v>
+      </c>
+      <c r="O2" t="n" s="0">
+        <v>603900.0</v>
+      </c>
+      <c r="P2" t="n" s="0">
+        <v>627400.0</v>
+      </c>
+      <c r="Q2" t="n" s="0">
+        <v>1285700.0</v>
+      </c>
+      <c r="R2" t="n" s="0">
+        <v>698000.0</v>
+      </c>
+      <c r="S2" t="n" s="0">
+        <v>571600.0</v>
+      </c>
+      <c r="T2" t="n" s="0">
+        <v>583600.0</v>
+      </c>
+      <c r="U2" t="n" s="0">
         <v>1168300.0</v>
       </c>
-      <c r="M2" t="n" s="0">
-        <v>1130400.0</v>
-      </c>
-      <c r="N2" t="n" s="0">
-        <v>896800.0</v>
-      </c>
-      <c r="O2" t="n" s="0">
-        <v>894100.0</v>
-      </c>
-      <c r="P2" t="n" s="0">
-        <v>1244700.0</v>
-      </c>
-      <c r="Q2" t="n" s="0">
-        <v>577100.0</v>
-      </c>
-      <c r="R2" t="n" s="0">
-        <v>1186400.0</v>
-      </c>
-      <c r="S2" t="n" s="0">
-        <v>577100.0</v>
-      </c>
-      <c r="T2" t="n" s="0">
-        <v>612400.0</v>
-      </c>
-      <c r="U2" t="n" s="0">
-        <v>587100.0</v>
-      </c>
       <c r="V2" t="n" s="0">
-        <v>585500.0</v>
+        <v>1161600.0</v>
       </c>
       <c r="W2" t="n" s="0">
-        <v>1199600.0</v>
+        <v>576000.0</v>
       </c>
     </row>
     <row r="3">
@@ -305,64 +305,64 @@
         <v>1000.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>424600.0</v>
+        <v>297300.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>94500.0</v>
+        <v>305400.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>334900.0</v>
+        <v>94900.0</v>
       </c>
       <c r="G3" t="n" s="0">
-        <v>308500.0</v>
+        <v>193000.0</v>
       </c>
       <c r="H3" t="n" s="0">
-        <v>320400.0</v>
+        <v>94600.0</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>110000.0</v>
+        <v>95300.0</v>
       </c>
       <c r="J3" t="n" s="0">
-        <v>166500.0</v>
+        <v>160000.0</v>
       </c>
       <c r="K3" t="n" s="0">
-        <v>96000.0</v>
+        <v>94300.0</v>
       </c>
       <c r="L3" t="n" s="0">
-        <v>303800.0</v>
+        <v>94900.0</v>
       </c>
       <c r="M3" t="n" s="0">
-        <v>94400.0</v>
+        <v>94700.0</v>
       </c>
       <c r="N3" t="n" s="0">
-        <v>99200.0</v>
+        <v>193600.0</v>
       </c>
       <c r="O3" t="n" s="0">
-        <v>97700.0</v>
+        <v>95300.0</v>
       </c>
       <c r="P3" t="n" s="0">
-        <v>320300.0</v>
+        <v>95000.0</v>
       </c>
       <c r="Q3" t="n" s="0">
-        <v>97600.0</v>
+        <v>299100.0</v>
       </c>
       <c r="R3" t="n" s="0">
-        <v>104800.0</v>
+        <v>213800.0</v>
       </c>
       <c r="S3" t="n" s="0">
-        <v>109200.0</v>
+        <v>98100.0</v>
       </c>
       <c r="T3" t="n" s="0">
-        <v>96000.0</v>
+        <v>95400.0</v>
       </c>
       <c r="U3" t="n" s="0">
-        <v>104600.0</v>
+        <v>325700.0</v>
       </c>
       <c r="V3" t="n" s="0">
         <v>99900.0</v>
       </c>
       <c r="W3" t="n" s="0">
-        <v>263000.0</v>
+        <v>191700.0</v>
       </c>
     </row>
     <row r="4">
@@ -376,64 +376,64 @@
         <v>1000.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>3094100.0</v>
+        <v>314200.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>681800.0</v>
+        <v>351500.0</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>776100.0</v>
+        <v>669700.0</v>
       </c>
       <c r="G4" t="n" s="0">
-        <v>651400.0</v>
+        <v>598900.0</v>
       </c>
       <c r="H4" t="n" s="0">
-        <v>324500.0</v>
+        <v>594800.0</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>707700.0</v>
+        <v>606300.0</v>
       </c>
       <c r="J4" t="n" s="0">
-        <v>806900.0</v>
+        <v>665200.0</v>
       </c>
       <c r="K4" t="n" s="0">
-        <v>606700.0</v>
+        <v>594700.0</v>
       </c>
       <c r="L4" t="n" s="0">
-        <v>675600.0</v>
+        <v>594600.0</v>
       </c>
       <c r="M4" t="n" s="0">
-        <v>596600.0</v>
+        <v>651900.0</v>
       </c>
       <c r="N4" t="n" s="0">
-        <v>596000.0</v>
+        <v>594500.0</v>
       </c>
       <c r="O4" t="n" s="0">
-        <v>603300.0</v>
+        <v>332000.0</v>
       </c>
       <c r="P4" t="n" s="0">
-        <v>558900.0</v>
+        <v>612100.0</v>
       </c>
       <c r="Q4" t="n" s="0">
-        <v>711500.0</v>
+        <v>608300.0</v>
       </c>
       <c r="R4" t="n" s="0">
-        <v>597800.0</v>
+        <v>606400.0</v>
       </c>
       <c r="S4" t="n" s="0">
-        <v>599600.0</v>
+        <v>647200.0</v>
       </c>
       <c r="T4" t="n" s="0">
-        <v>888200.0</v>
+        <v>818200.0</v>
       </c>
       <c r="U4" t="n" s="0">
-        <v>510300.0</v>
+        <v>598300.0</v>
       </c>
       <c r="V4" t="n" s="0">
-        <v>606400.0</v>
+        <v>594200.0</v>
       </c>
       <c r="W4" t="n" s="0">
-        <v>810300.0</v>
+        <v>642800.0</v>
       </c>
     </row>
     <row r="5">
@@ -447,64 +447,64 @@
         <v>1000.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>1438200.0</v>
+        <v>95000.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>415800.0</v>
+        <v>93900.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>1361000.0</v>
+        <v>81200.0</v>
       </c>
       <c r="G5" t="n" s="0">
-        <v>277400.0</v>
+        <v>46700.0</v>
       </c>
       <c r="H5" t="n" s="0">
-        <v>96700.0</v>
+        <v>45300.0</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>84800.0</v>
+        <v>44900.0</v>
       </c>
       <c r="J5" t="n" s="0">
-        <v>94500.0</v>
+        <v>53700.0</v>
       </c>
       <c r="K5" t="n" s="0">
-        <v>46400.0</v>
+        <v>46700.0</v>
       </c>
       <c r="L5" t="n" s="0">
-        <v>45100.0</v>
+        <v>44800.0</v>
       </c>
       <c r="M5" t="n" s="0">
-        <v>45300.0</v>
+        <v>46300.0</v>
       </c>
       <c r="N5" t="n" s="0">
-        <v>47400.0</v>
+        <v>45600.0</v>
       </c>
       <c r="O5" t="n" s="0">
-        <v>44300.0</v>
+        <v>92300.0</v>
       </c>
       <c r="P5" t="n" s="0">
-        <v>46600.0</v>
+        <v>48000.0</v>
       </c>
       <c r="Q5" t="n" s="0">
-        <v>60400.0</v>
+        <v>47300.0</v>
       </c>
       <c r="R5" t="n" s="0">
+        <v>46500.0</v>
+      </c>
+      <c r="S5" t="n" s="0">
         <v>46200.0</v>
       </c>
-      <c r="S5" t="n" s="0">
-        <v>45000.0</v>
-      </c>
       <c r="T5" t="n" s="0">
-        <v>45800.0</v>
+        <v>47100.0</v>
       </c>
       <c r="U5" t="n" s="0">
         <v>51200.0</v>
       </c>
       <c r="V5" t="n" s="0">
-        <v>46500.0</v>
+        <v>50600.0</v>
       </c>
       <c r="W5" t="n" s="0">
-        <v>46000.0</v>
+        <v>51900.0</v>
       </c>
     </row>
     <row r="6">
@@ -518,28 +518,28 @@
         <v>1000.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>3800.0</v>
+        <v>2300.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>6000.0</v>
+        <v>1700.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>12600.0</v>
+        <v>1700.0</v>
       </c>
       <c r="G6" t="n" s="0">
-        <v>2700.0</v>
+        <v>1000.0</v>
       </c>
       <c r="H6" t="n" s="0">
-        <v>1200.0</v>
+        <v>1300.0</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>1700.0</v>
+        <v>900.0</v>
       </c>
       <c r="J6" t="n" s="0">
-        <v>2400.0</v>
+        <v>1500.0</v>
       </c>
       <c r="K6" t="n" s="0">
-        <v>1000.0</v>
+        <v>1300.0</v>
       </c>
       <c r="L6" t="n" s="0">
         <v>900.0</v>
@@ -548,34 +548,34 @@
         <v>800.0</v>
       </c>
       <c r="N6" t="n" s="0">
-        <v>900.0</v>
+        <v>1000.0</v>
       </c>
       <c r="O6" t="n" s="0">
-        <v>800.0</v>
+        <v>2500.0</v>
       </c>
       <c r="P6" t="n" s="0">
         <v>800.0</v>
       </c>
       <c r="Q6" t="n" s="0">
-        <v>1600.0</v>
+        <v>800.0</v>
       </c>
       <c r="R6" t="n" s="0">
         <v>800.0</v>
       </c>
       <c r="S6" t="n" s="0">
-        <v>800.0</v>
+        <v>1700.0</v>
       </c>
       <c r="T6" t="n" s="0">
         <v>800.0</v>
       </c>
       <c r="U6" t="n" s="0">
-        <v>1500.0</v>
+        <v>800.0</v>
       </c>
       <c r="V6" t="n" s="0">
+        <v>900.0</v>
+      </c>
+      <c r="W6" t="n" s="0">
         <v>700.0</v>
-      </c>
-      <c r="W6" t="n" s="0">
-        <v>800.0</v>
       </c>
     </row>
     <row r="7">
@@ -589,64 +589,64 @@
         <v>1000.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>1846600.0</v>
+        <v>93100.0</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>666100.0</v>
+        <v>160000.0</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>1911800.0</v>
+        <v>150700.0</v>
       </c>
       <c r="G7" t="n" s="0">
-        <v>424600.0</v>
+        <v>84900.0</v>
       </c>
       <c r="H7" t="n" s="0">
-        <v>96900.0</v>
+        <v>86100.0</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>151500.0</v>
+        <v>91100.0</v>
       </c>
       <c r="J7" t="n" s="0">
-        <v>108500.0</v>
+        <v>118500.0</v>
       </c>
       <c r="K7" t="n" s="0">
-        <v>90100.0</v>
+        <v>87400.0</v>
       </c>
       <c r="L7" t="n" s="0">
-        <v>170700.0</v>
+        <v>87200.0</v>
       </c>
       <c r="M7" t="n" s="0">
-        <v>87000.0</v>
+        <v>87400.0</v>
       </c>
       <c r="N7" t="n" s="0">
-        <v>86700.0</v>
+        <v>88400.0</v>
       </c>
       <c r="O7" t="n" s="0">
-        <v>86800.0</v>
+        <v>109700.0</v>
       </c>
       <c r="P7" t="n" s="0">
+        <v>89300.0</v>
+      </c>
+      <c r="Q7" t="n" s="0">
+        <v>85200.0</v>
+      </c>
+      <c r="R7" t="n" s="0">
         <v>87700.0</v>
       </c>
-      <c r="Q7" t="n" s="0">
-        <v>94900.0</v>
-      </c>
-      <c r="R7" t="n" s="0">
-        <v>86300.0</v>
-      </c>
       <c r="S7" t="n" s="0">
-        <v>85400.0</v>
+        <v>181800.0</v>
       </c>
       <c r="T7" t="n" s="0">
-        <v>122900.0</v>
+        <v>87600.0</v>
       </c>
       <c r="U7" t="n" s="0">
-        <v>99400.0</v>
+        <v>92700.0</v>
       </c>
       <c r="V7" t="n" s="0">
-        <v>193100.0</v>
+        <v>87200.0</v>
       </c>
       <c r="W7" t="n" s="0">
-        <v>89200.0</v>
+        <v>97100.0</v>
       </c>
     </row>
     <row r="8">
@@ -660,64 +660,64 @@
         <v>1000.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>1785500.0</v>
+        <v>269700.0</v>
       </c>
       <c r="E8" t="n" s="0">
-        <v>444300.0</v>
+        <v>224900.0</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>307000.0</v>
+        <v>295200.0</v>
       </c>
       <c r="G8" t="n" s="0">
-        <v>211900.0</v>
+        <v>212200.0</v>
       </c>
       <c r="H8" t="n" s="0">
-        <v>430900.0</v>
+        <v>354000.0</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>326400.0</v>
+        <v>274100.0</v>
       </c>
       <c r="J8" t="n" s="0">
-        <v>317100.0</v>
+        <v>222300.0</v>
       </c>
       <c r="K8" t="n" s="0">
-        <v>213000.0</v>
+        <v>212500.0</v>
       </c>
       <c r="L8" t="n" s="0">
-        <v>442200.0</v>
+        <v>210700.0</v>
       </c>
       <c r="M8" t="n" s="0">
-        <v>271300.0</v>
+        <v>218800.0</v>
       </c>
       <c r="N8" t="n" s="0">
-        <v>211800.0</v>
+        <v>212600.0</v>
       </c>
       <c r="O8" t="n" s="0">
-        <v>210200.0</v>
+        <v>254400.0</v>
       </c>
       <c r="P8" t="n" s="0">
-        <v>211900.0</v>
+        <v>215900.0</v>
       </c>
       <c r="Q8" t="n" s="0">
+        <v>211000.0</v>
+      </c>
+      <c r="R8" t="n" s="0">
+        <v>217700.0</v>
+      </c>
+      <c r="S8" t="n" s="0">
+        <v>456100.0</v>
+      </c>
+      <c r="T8" t="n" s="0">
+        <v>211700.0</v>
+      </c>
+      <c r="U8" t="n" s="0">
         <v>212100.0</v>
       </c>
-      <c r="R8" t="n" s="0">
-        <v>212900.0</v>
-      </c>
-      <c r="S8" t="n" s="0">
-        <v>211300.0</v>
-      </c>
-      <c r="T8" t="n" s="0">
-        <v>219600.0</v>
-      </c>
-      <c r="U8" t="n" s="0">
-        <v>254000.0</v>
-      </c>
       <c r="V8" t="n" s="0">
-        <v>227100.0</v>
+        <v>211500.0</v>
       </c>
       <c r="W8" t="n" s="0">
-        <v>220600.0</v>
+        <v>241900.0</v>
       </c>
     </row>
     <row r="9">
@@ -731,64 +731,64 @@
         <v>1000.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>738900.0</v>
+        <v>408100.0</v>
       </c>
       <c r="E9" t="n" s="0">
-        <v>174200.0</v>
+        <v>182200.0</v>
       </c>
       <c r="F9" t="n" s="0">
+        <v>179100.0</v>
+      </c>
+      <c r="G9" t="n" s="0">
         <v>175100.0</v>
       </c>
-      <c r="G9" t="n" s="0">
-        <v>281400.0</v>
-      </c>
       <c r="H9" t="n" s="0">
-        <v>262000.0</v>
+        <v>270700.0</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>274700.0</v>
+        <v>237200.0</v>
       </c>
       <c r="J9" t="n" s="0">
-        <v>415500.0</v>
+        <v>182400.0</v>
       </c>
       <c r="K9" t="n" s="0">
-        <v>176200.0</v>
+        <v>172600.0</v>
       </c>
       <c r="L9" t="n" s="0">
-        <v>320500.0</v>
+        <v>172800.0</v>
       </c>
       <c r="M9" t="n" s="0">
-        <v>251300.0</v>
+        <v>173600.0</v>
       </c>
       <c r="N9" t="n" s="0">
-        <v>173100.0</v>
+        <v>174300.0</v>
       </c>
       <c r="O9" t="n" s="0">
-        <v>173700.0</v>
+        <v>201100.0</v>
       </c>
       <c r="P9" t="n" s="0">
-        <v>176900.0</v>
+        <v>172700.0</v>
       </c>
       <c r="Q9" t="n" s="0">
-        <v>173500.0</v>
+        <v>172800.0</v>
       </c>
       <c r="R9" t="n" s="0">
-        <v>177200.0</v>
+        <v>172700.0</v>
       </c>
       <c r="S9" t="n" s="0">
-        <v>176000.0</v>
+        <v>419800.0</v>
       </c>
       <c r="T9" t="n" s="0">
-        <v>174000.0</v>
+        <v>173300.0</v>
       </c>
       <c r="U9" t="n" s="0">
-        <v>173400.0</v>
+        <v>172900.0</v>
       </c>
       <c r="V9" t="n" s="0">
-        <v>198700.0</v>
+        <v>179700.0</v>
       </c>
       <c r="W9" t="n" s="0">
-        <v>172700.0</v>
+        <v>444600.0</v>
       </c>
     </row>
     <row r="10">
@@ -802,64 +802,64 @@
         <v>1000.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>2390800.0</v>
+        <v>1172800.0</v>
       </c>
       <c r="E10" t="n" s="0">
-        <v>888800.0</v>
+        <v>896500.0</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>825900.0</v>
+        <v>995600.0</v>
       </c>
       <c r="G10" t="n" s="0">
-        <v>918900.0</v>
+        <v>831100.0</v>
       </c>
       <c r="H10" t="n" s="0">
-        <v>1102800.0</v>
+        <v>1022600.0</v>
       </c>
       <c r="I10" t="n" s="0">
-        <v>834900.0</v>
+        <v>1124300.0</v>
       </c>
       <c r="J10" t="n" s="0">
-        <v>850100.0</v>
+        <v>866600.0</v>
       </c>
       <c r="K10" t="n" s="0">
-        <v>902900.0</v>
+        <v>829200.0</v>
       </c>
       <c r="L10" t="n" s="0">
-        <v>852100.0</v>
+        <v>823000.0</v>
       </c>
       <c r="M10" t="n" s="0">
-        <v>842000.0</v>
+        <v>1065500.0</v>
       </c>
       <c r="N10" t="n" s="0">
-        <v>822600.0</v>
+        <v>932400.0</v>
       </c>
       <c r="O10" t="n" s="0">
-        <v>821700.0</v>
+        <v>863600.0</v>
       </c>
       <c r="P10" t="n" s="0">
-        <v>856500.0</v>
+        <v>826700.0</v>
       </c>
       <c r="Q10" t="n" s="0">
-        <v>827100.0</v>
+        <v>974300.0</v>
       </c>
       <c r="R10" t="n" s="0">
-        <v>821900.0</v>
+        <v>834800.0</v>
       </c>
       <c r="S10" t="n" s="0">
-        <v>821600.0</v>
+        <v>1087300.0</v>
       </c>
       <c r="T10" t="n" s="0">
-        <v>826800.0</v>
+        <v>832100.0</v>
       </c>
       <c r="U10" t="n" s="0">
-        <v>835100.0</v>
+        <v>852300.0</v>
       </c>
       <c r="V10" t="n" s="0">
-        <v>830000.0</v>
+        <v>839100.0</v>
       </c>
       <c r="W10" t="n" s="0">
-        <v>868400.0</v>
+        <v>1186200.0</v>
       </c>
     </row>
     <row r="11">
@@ -873,64 +873,64 @@
         <v>1000.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>427700.0</v>
+        <v>172100.0</v>
       </c>
       <c r="E11" t="n" s="0">
-        <v>102900.0</v>
+        <v>82100.0</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>189400.0</v>
+        <v>111800.0</v>
       </c>
       <c r="G11" t="n" s="0">
-        <v>95500.0</v>
+        <v>75300.0</v>
       </c>
       <c r="H11" t="n" s="0">
-        <v>93800.0</v>
+        <v>75700.0</v>
       </c>
       <c r="I11" t="n" s="0">
-        <v>106700.0</v>
+        <v>121700.0</v>
       </c>
       <c r="J11" t="n" s="0">
-        <v>114400.0</v>
+        <v>77400.0</v>
       </c>
       <c r="K11" t="n" s="0">
-        <v>72400.0</v>
+        <v>87100.0</v>
       </c>
       <c r="L11" t="n" s="0">
-        <v>79600.0</v>
+        <v>72500.0</v>
       </c>
       <c r="M11" t="n" s="0">
-        <v>102200.0</v>
+        <v>79500.0</v>
       </c>
       <c r="N11" t="n" s="0">
-        <v>83100.0</v>
+        <v>74700.0</v>
       </c>
       <c r="O11" t="n" s="0">
-        <v>79400.0</v>
+        <v>93700.0</v>
       </c>
       <c r="P11" t="n" s="0">
-        <v>97800.0</v>
+        <v>72100.0</v>
       </c>
       <c r="Q11" t="n" s="0">
-        <v>75700.0</v>
+        <v>144400.0</v>
       </c>
       <c r="R11" t="n" s="0">
-        <v>74300.0</v>
+        <v>75000.0</v>
       </c>
       <c r="S11" t="n" s="0">
-        <v>87500.0</v>
+        <v>73200.0</v>
       </c>
       <c r="T11" t="n" s="0">
-        <v>70600.0</v>
+        <v>76100.0</v>
       </c>
       <c r="U11" t="n" s="0">
-        <v>187100.0</v>
+        <v>109900.0</v>
       </c>
       <c r="V11" t="n" s="0">
-        <v>70900.0</v>
+        <v>73000.0</v>
       </c>
       <c r="W11" t="n" s="0">
-        <v>86600.0</v>
+        <v>139300.0</v>
       </c>
     </row>
     <row r="12">
@@ -944,64 +944,64 @@
         <v>1000.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>69600.0</v>
+        <v>85500.0</v>
       </c>
       <c r="E12" t="n" s="0">
-        <v>41800.0</v>
+        <v>59200.0</v>
       </c>
       <c r="F12" t="n" s="0">
-        <v>67600.0</v>
+        <v>36700.0</v>
       </c>
       <c r="G12" t="n" s="0">
-        <v>33900.0</v>
+        <v>24900.0</v>
       </c>
       <c r="H12" t="n" s="0">
-        <v>34300.0</v>
+        <v>31100.0</v>
       </c>
       <c r="I12" t="n" s="0">
-        <v>51200.0</v>
+        <v>51900.0</v>
       </c>
       <c r="J12" t="n" s="0">
-        <v>47600.0</v>
+        <v>5381800.0</v>
       </c>
       <c r="K12" t="n" s="0">
-        <v>30000.0</v>
+        <v>38800.0</v>
       </c>
       <c r="L12" t="n" s="0">
+        <v>30900.0</v>
+      </c>
+      <c r="M12" t="n" s="0">
+        <v>42600.0</v>
+      </c>
+      <c r="N12" t="n" s="0">
         <v>26200.0</v>
       </c>
-      <c r="M12" t="n" s="0">
-        <v>46800.0</v>
-      </c>
-      <c r="N12" t="n" s="0">
-        <v>40400.0</v>
-      </c>
       <c r="O12" t="n" s="0">
-        <v>27000.0</v>
+        <v>41500.0</v>
       </c>
       <c r="P12" t="n" s="0">
-        <v>47500.0</v>
+        <v>25100.0</v>
       </c>
       <c r="Q12" t="n" s="0">
-        <v>25800.0</v>
+        <v>64300.0</v>
       </c>
       <c r="R12" t="n" s="0">
-        <v>32400.0</v>
+        <v>33300.0</v>
       </c>
       <c r="S12" t="n" s="0">
-        <v>41900.0</v>
+        <v>33800.0</v>
       </c>
       <c r="T12" t="n" s="0">
-        <v>26300.0</v>
+        <v>27500.0</v>
       </c>
       <c r="U12" t="n" s="0">
-        <v>26300.0</v>
+        <v>43100.0</v>
       </c>
       <c r="V12" t="n" s="0">
-        <v>32700.0</v>
+        <v>37800.0</v>
       </c>
       <c r="W12" t="n" s="0">
-        <v>29500.0</v>
+        <v>54100.0</v>
       </c>
     </row>
     <row r="13">
@@ -1015,64 +1015,64 @@
         <v>1000.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>409500.0</v>
+        <v>57200.0</v>
       </c>
       <c r="E13" t="n" s="0">
-        <v>139300.0</v>
+        <v>92300.0</v>
       </c>
       <c r="F13" t="n" s="0">
-        <v>75700.0</v>
+        <v>56400.0</v>
       </c>
       <c r="G13" t="n" s="0">
-        <v>70300.0</v>
+        <v>35900.0</v>
       </c>
       <c r="H13" t="n" s="0">
-        <v>56100.0</v>
+        <v>36500.0</v>
       </c>
       <c r="I13" t="n" s="0">
-        <v>81300.0</v>
+        <v>75600.0</v>
       </c>
       <c r="J13" t="n" s="0">
-        <v>97700.0</v>
+        <v>42300.0</v>
       </c>
       <c r="K13" t="n" s="0">
-        <v>58900.0</v>
+        <v>56200.0</v>
       </c>
       <c r="L13" t="n" s="0">
-        <v>38400.0</v>
+        <v>41400.0</v>
       </c>
       <c r="M13" t="n" s="0">
-        <v>69300.0</v>
+        <v>37300.0</v>
       </c>
       <c r="N13" t="n" s="0">
-        <v>54400.0</v>
+        <v>60000.0</v>
       </c>
       <c r="O13" t="n" s="0">
-        <v>40700.0</v>
+        <v>55500.0</v>
       </c>
       <c r="P13" t="n" s="0">
-        <v>60600.0</v>
+        <v>35500.0</v>
       </c>
       <c r="Q13" t="n" s="0">
-        <v>39400.0</v>
+        <v>75900.0</v>
       </c>
       <c r="R13" t="n" s="0">
-        <v>49700.0</v>
+        <v>37300.0</v>
       </c>
       <c r="S13" t="n" s="0">
-        <v>50000.0</v>
+        <v>45200.0</v>
       </c>
       <c r="T13" t="n" s="0">
-        <v>38300.0</v>
+        <v>35100.0</v>
       </c>
       <c r="U13" t="n" s="0">
-        <v>37300.0</v>
+        <v>64900.0</v>
       </c>
       <c r="V13" t="n" s="0">
-        <v>38400.0</v>
+        <v>47600.0</v>
       </c>
       <c r="W13" t="n" s="0">
-        <v>40000.0</v>
+        <v>80300.0</v>
       </c>
     </row>
     <row r="14">
@@ -1086,64 +1086,64 @@
         <v>1000.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>615100.0</v>
+        <v>125200.0</v>
       </c>
       <c r="E14" t="n" s="0">
-        <v>126900.0</v>
+        <v>185300.0</v>
       </c>
       <c r="F14" t="n" s="0">
-        <v>113700.0</v>
+        <v>177600.0</v>
       </c>
       <c r="G14" t="n" s="0">
-        <v>109300.0</v>
+        <v>116600.0</v>
       </c>
       <c r="H14" t="n" s="0">
-        <v>105700.0</v>
+        <v>110900.0</v>
       </c>
       <c r="I14" t="n" s="0">
-        <v>144800.0</v>
+        <v>139900.0</v>
       </c>
       <c r="J14" t="n" s="0">
-        <v>147500.0</v>
+        <v>175400.0</v>
       </c>
       <c r="K14" t="n" s="0">
-        <v>131800.0</v>
+        <v>123200.0</v>
       </c>
       <c r="L14" t="n" s="0">
-        <v>245400.0</v>
+        <v>101800.0</v>
       </c>
       <c r="M14" t="n" s="0">
-        <v>135000.0</v>
+        <v>99300.0</v>
       </c>
       <c r="N14" t="n" s="0">
-        <v>97500.0</v>
+        <v>122900.0</v>
       </c>
       <c r="O14" t="n" s="0">
-        <v>95500.0</v>
+        <v>119300.0</v>
       </c>
       <c r="P14" t="n" s="0">
-        <v>103800.0</v>
+        <v>93100.0</v>
       </c>
       <c r="Q14" t="n" s="0">
-        <v>100100.0</v>
+        <v>137600.0</v>
       </c>
       <c r="R14" t="n" s="0">
-        <v>107700.0</v>
+        <v>96100.0</v>
       </c>
       <c r="S14" t="n" s="0">
-        <v>122400.0</v>
+        <v>102100.0</v>
       </c>
       <c r="T14" t="n" s="0">
-        <v>93500.0</v>
+        <v>96200.0</v>
       </c>
       <c r="U14" t="n" s="0">
-        <v>92900.0</v>
+        <v>130900.0</v>
       </c>
       <c r="V14" t="n" s="0">
-        <v>107000.0</v>
+        <v>97900.0</v>
       </c>
       <c r="W14" t="n" s="0">
-        <v>135700.0</v>
+        <v>151200.0</v>
       </c>
     </row>
     <row r="15">
@@ -1157,64 +1157,64 @@
         <v>1000.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>68600.0</v>
+        <v>57500.0</v>
       </c>
       <c r="E15" t="n" s="0">
-        <v>54500.0</v>
+        <v>100000.0</v>
       </c>
       <c r="F15" t="n" s="0">
-        <v>70500.0</v>
+        <v>99800.0</v>
       </c>
       <c r="G15" t="n" s="0">
-        <v>54800.0</v>
+        <v>51400.0</v>
       </c>
       <c r="H15" t="n" s="0">
-        <v>52200.0</v>
+        <v>97100.0</v>
       </c>
       <c r="I15" t="n" s="0">
-        <v>61500.0</v>
+        <v>85400.0</v>
       </c>
       <c r="J15" t="n" s="0">
-        <v>87700.0</v>
+        <v>57800.0</v>
       </c>
       <c r="K15" t="n" s="0">
-        <v>84300.0</v>
+        <v>79600.0</v>
       </c>
       <c r="L15" t="n" s="0">
-        <v>51900.0</v>
+        <v>43800.0</v>
       </c>
       <c r="M15" t="n" s="0">
-        <v>64100.0</v>
+        <v>45000.0</v>
       </c>
       <c r="N15" t="n" s="0">
-        <v>46600.0</v>
+        <v>69600.0</v>
       </c>
       <c r="O15" t="n" s="0">
-        <v>41700.0</v>
+        <v>61700.0</v>
       </c>
       <c r="P15" t="n" s="0">
-        <v>49700.0</v>
+        <v>46900.0</v>
       </c>
       <c r="Q15" t="n" s="0">
-        <v>40300.0</v>
+        <v>85700.0</v>
       </c>
       <c r="R15" t="n" s="0">
-        <v>69800.0</v>
+        <v>47400.0</v>
       </c>
       <c r="S15" t="n" s="0">
-        <v>53500.0</v>
+        <v>42100.0</v>
       </c>
       <c r="T15" t="n" s="0">
-        <v>47500.0</v>
+        <v>49000.0</v>
       </c>
       <c r="U15" t="n" s="0">
-        <v>40100.0</v>
+        <v>100100.0</v>
       </c>
       <c r="V15" t="n" s="0">
-        <v>45700.0</v>
+        <v>51400.0</v>
       </c>
       <c r="W15" t="n" s="0">
-        <v>55000.0</v>
+        <v>92100.0</v>
       </c>
     </row>
     <row r="16">
@@ -1228,64 +1228,64 @@
         <v>1000.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>324100.0</v>
+        <v>134300.0</v>
       </c>
       <c r="E16" t="n" s="0">
-        <v>77200.0</v>
+        <v>145200.0</v>
       </c>
       <c r="F16" t="n" s="0">
-        <v>133800.0</v>
+        <v>98200.0</v>
       </c>
       <c r="G16" t="n" s="0">
-        <v>130500.0</v>
+        <v>62400.0</v>
       </c>
       <c r="H16" t="n" s="0">
-        <v>79400.0</v>
+        <v>52400.0</v>
       </c>
       <c r="I16" t="n" s="0">
-        <v>81700.0</v>
+        <v>92200.0</v>
       </c>
       <c r="J16" t="n" s="0">
-        <v>106900.0</v>
+        <v>50400.0</v>
       </c>
       <c r="K16" t="n" s="0">
-        <v>58900.0</v>
+        <v>53600.0</v>
       </c>
       <c r="L16" t="n" s="0">
-        <v>77100.0</v>
+        <v>49000.0</v>
       </c>
       <c r="M16" t="n" s="0">
-        <v>88000.0</v>
+        <v>55100.0</v>
       </c>
       <c r="N16" t="n" s="0">
-        <v>50200.0</v>
+        <v>67500.0</v>
       </c>
       <c r="O16" t="n" s="0">
-        <v>91500.0</v>
+        <v>51900.0</v>
       </c>
       <c r="P16" t="n" s="0">
-        <v>70700.0</v>
+        <v>44400.0</v>
       </c>
       <c r="Q16" t="n" s="0">
-        <v>47000.0</v>
+        <v>93100.0</v>
       </c>
       <c r="R16" t="n" s="0">
-        <v>61300.0</v>
+        <v>46400.0</v>
       </c>
       <c r="S16" t="n" s="0">
-        <v>42100.0</v>
+        <v>47800.0</v>
       </c>
       <c r="T16" t="n" s="0">
-        <v>43900.0</v>
+        <v>42400.0</v>
       </c>
       <c r="U16" t="n" s="0">
-        <v>47100.0</v>
+        <v>69200.0</v>
       </c>
       <c r="V16" t="n" s="0">
-        <v>45500.0</v>
+        <v>45800.0</v>
       </c>
       <c r="W16" t="n" s="0">
-        <v>62800.0</v>
+        <v>94500.0</v>
       </c>
     </row>
   </sheetData>

--- a/excel/1000(n)/RAW_Dataset.xlsx
+++ b/excel/1000(n)/RAW_Dataset.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="32">
   <si>
     <t xml:space="preserve">Algorithm </t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>Trial 20</t>
+  </si>
+  <si>
+    <t>Average</t>
   </si>
 </sst>
 </file>
@@ -149,7 +152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -222,6 +225,9 @@
       <c r="W1" t="s" s="0">
         <v>30</v>
       </c>
+      <c r="X1" t="s" s="0">
+        <v>31</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
@@ -234,64 +240,67 @@
         <v>1000.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>1047900.0</v>
+        <v>1060400.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>1193000.0</v>
+        <v>810100.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>1061600.0</v>
+        <v>1070300.0</v>
       </c>
       <c r="G2" t="n" s="0">
-        <v>850300.0</v>
+        <v>1086900.0</v>
       </c>
       <c r="H2" t="n" s="0">
-        <v>1127100.0</v>
+        <v>1142100.0</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>571200.0</v>
+        <v>1122300.0</v>
       </c>
       <c r="J2" t="n" s="0">
-        <v>1171200.0</v>
+        <v>1139600.0</v>
       </c>
       <c r="K2" t="n" s="0">
-        <v>589600.0</v>
+        <v>1146800.0</v>
       </c>
       <c r="L2" t="n" s="0">
-        <v>770700.0</v>
+        <v>777500.0</v>
       </c>
       <c r="M2" t="n" s="0">
-        <v>1141400.0</v>
+        <v>714700.0</v>
       </c>
       <c r="N2" t="n" s="0">
-        <v>566600.0</v>
+        <v>580800.0</v>
       </c>
       <c r="O2" t="n" s="0">
-        <v>603900.0</v>
+        <v>1110800.0</v>
       </c>
       <c r="P2" t="n" s="0">
-        <v>627400.0</v>
+        <v>1162000.0</v>
       </c>
       <c r="Q2" t="n" s="0">
-        <v>1285700.0</v>
+        <v>1120700.0</v>
       </c>
       <c r="R2" t="n" s="0">
-        <v>698000.0</v>
+        <v>587700.0</v>
       </c>
       <c r="S2" t="n" s="0">
-        <v>571600.0</v>
+        <v>1119500.0</v>
       </c>
       <c r="T2" t="n" s="0">
-        <v>583600.0</v>
+        <v>575400.0</v>
       </c>
       <c r="U2" t="n" s="0">
-        <v>1168300.0</v>
+        <v>595900.0</v>
       </c>
       <c r="V2" t="n" s="0">
-        <v>1161600.0</v>
+        <v>873900.0</v>
       </c>
       <c r="W2" t="n" s="0">
-        <v>576000.0</v>
+        <v>1122800.0</v>
+      </c>
+      <c r="X2" t="n" s="0">
+        <v>946010.0</v>
       </c>
     </row>
     <row r="3">
@@ -305,64 +314,67 @@
         <v>1000.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>297300.0</v>
+        <v>106500.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>305400.0</v>
+        <v>328000.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>94900.0</v>
+        <v>303000.0</v>
       </c>
       <c r="G3" t="n" s="0">
-        <v>193000.0</v>
+        <v>314000.0</v>
       </c>
       <c r="H3" t="n" s="0">
+        <v>317700.0</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>115000.0</v>
+      </c>
+      <c r="J3" t="n" s="0">
+        <v>311200.0</v>
+      </c>
+      <c r="K3" t="n" s="0">
+        <v>99300.0</v>
+      </c>
+      <c r="L3" t="n" s="0">
+        <v>211200.0</v>
+      </c>
+      <c r="M3" t="n" s="0">
+        <v>97300.0</v>
+      </c>
+      <c r="N3" t="n" s="0">
+        <v>141400.0</v>
+      </c>
+      <c r="O3" t="n" s="0">
         <v>94600.0</v>
       </c>
-      <c r="I3" t="n" s="0">
-        <v>95300.0</v>
-      </c>
-      <c r="J3" t="n" s="0">
-        <v>160000.0</v>
-      </c>
-      <c r="K3" t="n" s="0">
-        <v>94300.0</v>
-      </c>
-      <c r="L3" t="n" s="0">
-        <v>94900.0</v>
-      </c>
-      <c r="M3" t="n" s="0">
-        <v>94700.0</v>
-      </c>
-      <c r="N3" t="n" s="0">
-        <v>193600.0</v>
-      </c>
-      <c r="O3" t="n" s="0">
-        <v>95300.0</v>
-      </c>
       <c r="P3" t="n" s="0">
-        <v>95000.0</v>
+        <v>113900.0</v>
       </c>
       <c r="Q3" t="n" s="0">
-        <v>299100.0</v>
+        <v>94600.0</v>
       </c>
       <c r="R3" t="n" s="0">
-        <v>213800.0</v>
+        <v>96300.0</v>
       </c>
       <c r="S3" t="n" s="0">
-        <v>98100.0</v>
+        <v>95400.0</v>
       </c>
       <c r="T3" t="n" s="0">
-        <v>95400.0</v>
+        <v>94100.0</v>
       </c>
       <c r="U3" t="n" s="0">
-        <v>325700.0</v>
+        <v>100800.0</v>
       </c>
       <c r="V3" t="n" s="0">
-        <v>99900.0</v>
+        <v>192900.0</v>
       </c>
       <c r="W3" t="n" s="0">
-        <v>191700.0</v>
+        <v>299600.0</v>
+      </c>
+      <c r="X3" t="n" s="0">
+        <v>176340.0</v>
       </c>
     </row>
     <row r="4">
@@ -376,64 +388,67 @@
         <v>1000.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>314200.0</v>
+        <v>601700.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>351500.0</v>
+        <v>305500.0</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>669700.0</v>
+        <v>305200.0</v>
       </c>
       <c r="G4" t="n" s="0">
-        <v>598900.0</v>
+        <v>316700.0</v>
       </c>
       <c r="H4" t="n" s="0">
-        <v>594800.0</v>
+        <v>321500.0</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>606300.0</v>
+        <v>630800.0</v>
       </c>
       <c r="J4" t="n" s="0">
-        <v>665200.0</v>
+        <v>329100.0</v>
       </c>
       <c r="K4" t="n" s="0">
-        <v>594700.0</v>
+        <v>686800.0</v>
       </c>
       <c r="L4" t="n" s="0">
-        <v>594600.0</v>
+        <v>722900.0</v>
       </c>
       <c r="M4" t="n" s="0">
-        <v>651900.0</v>
+        <v>614900.0</v>
       </c>
       <c r="N4" t="n" s="0">
-        <v>594500.0</v>
+        <v>601000.0</v>
       </c>
       <c r="O4" t="n" s="0">
-        <v>332000.0</v>
+        <v>733800.0</v>
       </c>
       <c r="P4" t="n" s="0">
-        <v>612100.0</v>
+        <v>596100.0</v>
       </c>
       <c r="Q4" t="n" s="0">
-        <v>608300.0</v>
+        <v>592900.0</v>
       </c>
       <c r="R4" t="n" s="0">
-        <v>606400.0</v>
+        <v>600100.0</v>
       </c>
       <c r="S4" t="n" s="0">
-        <v>647200.0</v>
+        <v>613800.0</v>
       </c>
       <c r="T4" t="n" s="0">
-        <v>818200.0</v>
+        <v>600200.0</v>
       </c>
       <c r="U4" t="n" s="0">
-        <v>598300.0</v>
+        <v>603000.0</v>
       </c>
       <c r="V4" t="n" s="0">
-        <v>594200.0</v>
+        <v>595000.0</v>
       </c>
       <c r="W4" t="n" s="0">
-        <v>642800.0</v>
+        <v>330100.0</v>
+      </c>
+      <c r="X4" t="n" s="0">
+        <v>535055.0</v>
       </c>
     </row>
     <row r="5">
@@ -447,64 +462,67 @@
         <v>1000.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>95000.0</v>
+        <v>94300.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>93900.0</v>
+        <v>96300.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>81200.0</v>
+        <v>98800.0</v>
       </c>
       <c r="G5" t="n" s="0">
-        <v>46700.0</v>
+        <v>94000.0</v>
       </c>
       <c r="H5" t="n" s="0">
-        <v>45300.0</v>
+        <v>91900.0</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>44900.0</v>
+        <v>91000.0</v>
       </c>
       <c r="J5" t="n" s="0">
-        <v>53700.0</v>
+        <v>55100.0</v>
       </c>
       <c r="K5" t="n" s="0">
-        <v>46700.0</v>
+        <v>47700.0</v>
       </c>
       <c r="L5" t="n" s="0">
-        <v>44800.0</v>
+        <v>83300.0</v>
       </c>
       <c r="M5" t="n" s="0">
-        <v>46300.0</v>
+        <v>47700.0</v>
       </c>
       <c r="N5" t="n" s="0">
-        <v>45600.0</v>
+        <v>45700.0</v>
       </c>
       <c r="O5" t="n" s="0">
-        <v>92300.0</v>
+        <v>44100.0</v>
       </c>
       <c r="P5" t="n" s="0">
-        <v>48000.0</v>
+        <v>48400.0</v>
       </c>
       <c r="Q5" t="n" s="0">
-        <v>47300.0</v>
+        <v>45900.0</v>
       </c>
       <c r="R5" t="n" s="0">
-        <v>46500.0</v>
+        <v>46100.0</v>
       </c>
       <c r="S5" t="n" s="0">
-        <v>46200.0</v>
+        <v>45200.0</v>
       </c>
       <c r="T5" t="n" s="0">
-        <v>47100.0</v>
+        <v>46900.0</v>
       </c>
       <c r="U5" t="n" s="0">
-        <v>51200.0</v>
+        <v>101000.0</v>
       </c>
       <c r="V5" t="n" s="0">
-        <v>50600.0</v>
+        <v>46400.0</v>
       </c>
       <c r="W5" t="n" s="0">
-        <v>51900.0</v>
+        <v>100000.0</v>
+      </c>
+      <c r="X5" t="n" s="0">
+        <v>68490.0</v>
       </c>
     </row>
     <row r="6">
@@ -518,64 +536,67 @@
         <v>1000.0</v>
       </c>
       <c r="D6" t="n" s="0">
+        <v>2700.0</v>
+      </c>
+      <c r="E6" t="n" s="0">
+        <v>2400.0</v>
+      </c>
+      <c r="F6" t="n" s="0">
         <v>2300.0</v>
       </c>
-      <c r="E6" t="n" s="0">
+      <c r="G6" t="n" s="0">
+        <v>1600.0</v>
+      </c>
+      <c r="H6" t="n" s="0">
+        <v>4200.0</v>
+      </c>
+      <c r="I6" t="n" s="0">
         <v>1700.0</v>
       </c>
-      <c r="F6" t="n" s="0">
-        <v>1700.0</v>
-      </c>
-      <c r="G6" t="n" s="0">
-        <v>1000.0</v>
-      </c>
-      <c r="H6" t="n" s="0">
-        <v>1300.0</v>
-      </c>
-      <c r="I6" t="n" s="0">
+      <c r="J6" t="n" s="0">
+        <v>1400.0</v>
+      </c>
+      <c r="K6" t="n" s="0">
         <v>900.0</v>
       </c>
-      <c r="J6" t="n" s="0">
-        <v>1500.0</v>
-      </c>
-      <c r="K6" t="n" s="0">
-        <v>1300.0</v>
-      </c>
       <c r="L6" t="n" s="0">
+        <v>2100.0</v>
+      </c>
+      <c r="M6" t="n" s="0">
         <v>900.0</v>
       </c>
-      <c r="M6" t="n" s="0">
+      <c r="N6" t="n" s="0">
         <v>800.0</v>
       </c>
-      <c r="N6" t="n" s="0">
-        <v>1000.0</v>
-      </c>
       <c r="O6" t="n" s="0">
-        <v>2500.0</v>
+        <v>900.0</v>
       </c>
       <c r="P6" t="n" s="0">
         <v>800.0</v>
       </c>
       <c r="Q6" t="n" s="0">
-        <v>800.0</v>
+        <v>900.0</v>
       </c>
       <c r="R6" t="n" s="0">
-        <v>800.0</v>
+        <v>700.0</v>
       </c>
       <c r="S6" t="n" s="0">
-        <v>1700.0</v>
+        <v>1400.0</v>
       </c>
       <c r="T6" t="n" s="0">
         <v>800.0</v>
       </c>
       <c r="U6" t="n" s="0">
-        <v>800.0</v>
+        <v>1400.0</v>
       </c>
       <c r="V6" t="n" s="0">
-        <v>900.0</v>
+        <v>700.0</v>
       </c>
       <c r="W6" t="n" s="0">
-        <v>700.0</v>
+        <v>1500.0</v>
+      </c>
+      <c r="X6" t="n" s="0">
+        <v>1505.0</v>
       </c>
     </row>
     <row r="7">
@@ -589,64 +610,67 @@
         <v>1000.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>93100.0</v>
+        <v>168200.0</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>160000.0</v>
+        <v>185300.0</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>150700.0</v>
+        <v>203800.0</v>
       </c>
       <c r="G7" t="n" s="0">
-        <v>84900.0</v>
+        <v>182000.0</v>
       </c>
       <c r="H7" t="n" s="0">
-        <v>86100.0</v>
+        <v>120600.0</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>91100.0</v>
+        <v>186000.0</v>
       </c>
       <c r="J7" t="n" s="0">
-        <v>118500.0</v>
+        <v>89800.0</v>
       </c>
       <c r="K7" t="n" s="0">
-        <v>87400.0</v>
+        <v>85300.0</v>
       </c>
       <c r="L7" t="n" s="0">
-        <v>87200.0</v>
+        <v>160500.0</v>
       </c>
       <c r="M7" t="n" s="0">
-        <v>87400.0</v>
+        <v>88200.0</v>
       </c>
       <c r="N7" t="n" s="0">
-        <v>88400.0</v>
+        <v>89700.0</v>
       </c>
       <c r="O7" t="n" s="0">
-        <v>109700.0</v>
+        <v>85900.0</v>
       </c>
       <c r="P7" t="n" s="0">
-        <v>89300.0</v>
+        <v>85800.0</v>
       </c>
       <c r="Q7" t="n" s="0">
-        <v>85200.0</v>
+        <v>89600.0</v>
       </c>
       <c r="R7" t="n" s="0">
-        <v>87700.0</v>
+        <v>85700.0</v>
       </c>
       <c r="S7" t="n" s="0">
-        <v>181800.0</v>
+        <v>124000.0</v>
       </c>
       <c r="T7" t="n" s="0">
-        <v>87600.0</v>
+        <v>86800.0</v>
       </c>
       <c r="U7" t="n" s="0">
-        <v>92700.0</v>
+        <v>187800.0</v>
       </c>
       <c r="V7" t="n" s="0">
-        <v>87200.0</v>
+        <v>89600.0</v>
       </c>
       <c r="W7" t="n" s="0">
-        <v>97100.0</v>
+        <v>181900.0</v>
+      </c>
+      <c r="X7" t="n" s="0">
+        <v>128825.0</v>
       </c>
     </row>
     <row r="8">
@@ -660,64 +684,67 @@
         <v>1000.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>269700.0</v>
+        <v>452400.0</v>
       </c>
       <c r="E8" t="n" s="0">
-        <v>224900.0</v>
+        <v>450700.0</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>295200.0</v>
+        <v>455300.0</v>
       </c>
       <c r="G8" t="n" s="0">
-        <v>212200.0</v>
+        <v>441500.0</v>
       </c>
       <c r="H8" t="n" s="0">
-        <v>354000.0</v>
+        <v>269500.0</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>274100.0</v>
+        <v>441600.0</v>
       </c>
       <c r="J8" t="n" s="0">
-        <v>222300.0</v>
+        <v>212500.0</v>
       </c>
       <c r="K8" t="n" s="0">
-        <v>212500.0</v>
+        <v>229400.0</v>
       </c>
       <c r="L8" t="n" s="0">
+        <v>330500.0</v>
+      </c>
+      <c r="M8" t="n" s="0">
+        <v>211800.0</v>
+      </c>
+      <c r="N8" t="n" s="0">
+        <v>212700.0</v>
+      </c>
+      <c r="O8" t="n" s="0">
+        <v>217100.0</v>
+      </c>
+      <c r="P8" t="n" s="0">
+        <v>211900.0</v>
+      </c>
+      <c r="Q8" t="n" s="0">
+        <v>211600.0</v>
+      </c>
+      <c r="R8" t="n" s="0">
+        <v>213700.0</v>
+      </c>
+      <c r="S8" t="n" s="0">
+        <v>214800.0</v>
+      </c>
+      <c r="T8" t="n" s="0">
+        <v>211600.0</v>
+      </c>
+      <c r="U8" t="n" s="0">
+        <v>441900.0</v>
+      </c>
+      <c r="V8" t="n" s="0">
         <v>210700.0</v>
       </c>
-      <c r="M8" t="n" s="0">
-        <v>218800.0</v>
-      </c>
-      <c r="N8" t="n" s="0">
-        <v>212600.0</v>
-      </c>
-      <c r="O8" t="n" s="0">
-        <v>254400.0</v>
-      </c>
-      <c r="P8" t="n" s="0">
-        <v>215900.0</v>
-      </c>
-      <c r="Q8" t="n" s="0">
-        <v>211000.0</v>
-      </c>
-      <c r="R8" t="n" s="0">
-        <v>217700.0</v>
-      </c>
-      <c r="S8" t="n" s="0">
-        <v>456100.0</v>
-      </c>
-      <c r="T8" t="n" s="0">
-        <v>211700.0</v>
-      </c>
-      <c r="U8" t="n" s="0">
-        <v>212100.0</v>
-      </c>
-      <c r="V8" t="n" s="0">
-        <v>211500.0</v>
-      </c>
       <c r="W8" t="n" s="0">
-        <v>241900.0</v>
+        <v>445900.0</v>
+      </c>
+      <c r="X8" t="n" s="0">
+        <v>304355.0</v>
       </c>
     </row>
     <row r="9">
@@ -731,64 +758,67 @@
         <v>1000.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>408100.0</v>
+        <v>276700.0</v>
       </c>
       <c r="E9" t="n" s="0">
-        <v>182200.0</v>
+        <v>410000.0</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>179100.0</v>
+        <v>440700.0</v>
       </c>
       <c r="G9" t="n" s="0">
-        <v>175100.0</v>
+        <v>414200.0</v>
       </c>
       <c r="H9" t="n" s="0">
-        <v>270700.0</v>
+        <v>174600.0</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>237200.0</v>
+        <v>411200.0</v>
       </c>
       <c r="J9" t="n" s="0">
-        <v>182400.0</v>
+        <v>313800.0</v>
       </c>
       <c r="K9" t="n" s="0">
-        <v>172600.0</v>
+        <v>187000.0</v>
       </c>
       <c r="L9" t="n" s="0">
-        <v>172800.0</v>
+        <v>286800.0</v>
       </c>
       <c r="M9" t="n" s="0">
-        <v>173600.0</v>
+        <v>177400.0</v>
       </c>
       <c r="N9" t="n" s="0">
-        <v>174300.0</v>
+        <v>173800.0</v>
       </c>
       <c r="O9" t="n" s="0">
-        <v>201100.0</v>
+        <v>173300.0</v>
       </c>
       <c r="P9" t="n" s="0">
-        <v>172700.0</v>
+        <v>172900.0</v>
       </c>
       <c r="Q9" t="n" s="0">
-        <v>172800.0</v>
+        <v>178100.0</v>
       </c>
       <c r="R9" t="n" s="0">
         <v>172700.0</v>
       </c>
       <c r="S9" t="n" s="0">
-        <v>419800.0</v>
+        <v>173000.0</v>
       </c>
       <c r="T9" t="n" s="0">
-        <v>173300.0</v>
+        <v>172800.0</v>
       </c>
       <c r="U9" t="n" s="0">
+        <v>415900.0</v>
+      </c>
+      <c r="V9" t="n" s="0">
         <v>172900.0</v>
       </c>
-      <c r="V9" t="n" s="0">
-        <v>179700.0</v>
-      </c>
       <c r="W9" t="n" s="0">
-        <v>444600.0</v>
+        <v>418200.0</v>
+      </c>
+      <c r="X9" t="n" s="0">
+        <v>265800.0</v>
       </c>
     </row>
     <row r="10">
@@ -802,64 +832,67 @@
         <v>1000.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>1172800.0</v>
+        <v>843600.0</v>
       </c>
       <c r="E10" t="n" s="0">
-        <v>896500.0</v>
+        <v>1091800.0</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>995600.0</v>
+        <v>1125900.0</v>
       </c>
       <c r="G10" t="n" s="0">
-        <v>831100.0</v>
+        <v>1023200.0</v>
       </c>
       <c r="H10" t="n" s="0">
-        <v>1022600.0</v>
+        <v>823000.0</v>
       </c>
       <c r="I10" t="n" s="0">
-        <v>1124300.0</v>
+        <v>1123400.0</v>
       </c>
       <c r="J10" t="n" s="0">
-        <v>866600.0</v>
+        <v>846400.0</v>
       </c>
       <c r="K10" t="n" s="0">
-        <v>829200.0</v>
+        <v>857700.0</v>
       </c>
       <c r="L10" t="n" s="0">
-        <v>823000.0</v>
+        <v>858300.0</v>
       </c>
       <c r="M10" t="n" s="0">
-        <v>1065500.0</v>
+        <v>1003600.0</v>
       </c>
       <c r="N10" t="n" s="0">
-        <v>932400.0</v>
+        <v>1132400.0</v>
       </c>
       <c r="O10" t="n" s="0">
-        <v>863600.0</v>
+        <v>842500.0</v>
       </c>
       <c r="P10" t="n" s="0">
-        <v>826700.0</v>
+        <v>861900.0</v>
       </c>
       <c r="Q10" t="n" s="0">
-        <v>974300.0</v>
+        <v>827400.0</v>
       </c>
       <c r="R10" t="n" s="0">
-        <v>834800.0</v>
+        <v>910300.0</v>
       </c>
       <c r="S10" t="n" s="0">
-        <v>1087300.0</v>
+        <v>824900.0</v>
       </c>
       <c r="T10" t="n" s="0">
-        <v>832100.0</v>
+        <v>826800.0</v>
       </c>
       <c r="U10" t="n" s="0">
-        <v>852300.0</v>
+        <v>1127400.0</v>
       </c>
       <c r="V10" t="n" s="0">
-        <v>839100.0</v>
+        <v>825900.0</v>
       </c>
       <c r="W10" t="n" s="0">
-        <v>1186200.0</v>
+        <v>1152300.0</v>
+      </c>
+      <c r="X10" t="n" s="0">
+        <v>946435.0</v>
       </c>
     </row>
     <row r="11">
@@ -873,64 +906,67 @@
         <v>1000.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>172100.0</v>
+        <v>143300.0</v>
       </c>
       <c r="E11" t="n" s="0">
-        <v>82100.0</v>
+        <v>162000.0</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>111800.0</v>
+        <v>297600.0</v>
       </c>
       <c r="G11" t="n" s="0">
-        <v>75300.0</v>
+        <v>104800.0</v>
       </c>
       <c r="H11" t="n" s="0">
-        <v>75700.0</v>
+        <v>70600.0</v>
       </c>
       <c r="I11" t="n" s="0">
-        <v>121700.0</v>
+        <v>130900.0</v>
       </c>
       <c r="J11" t="n" s="0">
-        <v>77400.0</v>
+        <v>102000.0</v>
       </c>
       <c r="K11" t="n" s="0">
-        <v>87100.0</v>
+        <v>75500.0</v>
       </c>
       <c r="L11" t="n" s="0">
-        <v>72500.0</v>
+        <v>105400.0</v>
       </c>
       <c r="M11" t="n" s="0">
-        <v>79500.0</v>
+        <v>87200.0</v>
       </c>
       <c r="N11" t="n" s="0">
-        <v>74700.0</v>
+        <v>137400.0</v>
       </c>
       <c r="O11" t="n" s="0">
-        <v>93700.0</v>
+        <v>91500.0</v>
       </c>
       <c r="P11" t="n" s="0">
-        <v>72100.0</v>
+        <v>73100.0</v>
       </c>
       <c r="Q11" t="n" s="0">
-        <v>144400.0</v>
+        <v>73200.0</v>
       </c>
       <c r="R11" t="n" s="0">
-        <v>75000.0</v>
+        <v>78600.0</v>
       </c>
       <c r="S11" t="n" s="0">
-        <v>73200.0</v>
+        <v>75500.0</v>
       </c>
       <c r="T11" t="n" s="0">
-        <v>76100.0</v>
+        <v>73000.0</v>
       </c>
       <c r="U11" t="n" s="0">
-        <v>109900.0</v>
+        <v>76200.0</v>
       </c>
       <c r="V11" t="n" s="0">
-        <v>73000.0</v>
+        <v>71400.0</v>
       </c>
       <c r="W11" t="n" s="0">
-        <v>139300.0</v>
+        <v>125600.0</v>
+      </c>
+      <c r="X11" t="n" s="0">
+        <v>107740.0</v>
       </c>
     </row>
     <row r="12">
@@ -944,64 +980,67 @@
         <v>1000.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>85500.0</v>
+        <v>67200.0</v>
       </c>
       <c r="E12" t="n" s="0">
-        <v>59200.0</v>
+        <v>77800.0</v>
       </c>
       <c r="F12" t="n" s="0">
-        <v>36700.0</v>
+        <v>66000.0</v>
       </c>
       <c r="G12" t="n" s="0">
-        <v>24900.0</v>
+        <v>51800.0</v>
       </c>
       <c r="H12" t="n" s="0">
-        <v>31100.0</v>
+        <v>25600.0</v>
       </c>
       <c r="I12" t="n" s="0">
-        <v>51900.0</v>
+        <v>54800.0</v>
       </c>
       <c r="J12" t="n" s="0">
-        <v>5381800.0</v>
+        <v>62700.0</v>
       </c>
       <c r="K12" t="n" s="0">
-        <v>38800.0</v>
+        <v>27200.0</v>
       </c>
       <c r="L12" t="n" s="0">
-        <v>30900.0</v>
+        <v>30700.0</v>
       </c>
       <c r="M12" t="n" s="0">
-        <v>42600.0</v>
+        <v>34400.0</v>
       </c>
       <c r="N12" t="n" s="0">
+        <v>39500.0</v>
+      </c>
+      <c r="O12" t="n" s="0">
+        <v>52500.0</v>
+      </c>
+      <c r="P12" t="n" s="0">
+        <v>23900.0</v>
+      </c>
+      <c r="Q12" t="n" s="0">
+        <v>31500.0</v>
+      </c>
+      <c r="R12" t="n" s="0">
+        <v>32000.0</v>
+      </c>
+      <c r="S12" t="n" s="0">
+        <v>26500.0</v>
+      </c>
+      <c r="T12" t="n" s="0">
+        <v>26000.0</v>
+      </c>
+      <c r="U12" t="n" s="0">
         <v>26200.0</v>
       </c>
-      <c r="O12" t="n" s="0">
-        <v>41500.0</v>
-      </c>
-      <c r="P12" t="n" s="0">
-        <v>25100.0</v>
-      </c>
-      <c r="Q12" t="n" s="0">
-        <v>64300.0</v>
-      </c>
-      <c r="R12" t="n" s="0">
-        <v>33300.0</v>
-      </c>
-      <c r="S12" t="n" s="0">
-        <v>33800.0</v>
-      </c>
-      <c r="T12" t="n" s="0">
-        <v>27500.0</v>
-      </c>
-      <c r="U12" t="n" s="0">
-        <v>43100.0</v>
-      </c>
       <c r="V12" t="n" s="0">
-        <v>37800.0</v>
+        <v>28700.0</v>
       </c>
       <c r="W12" t="n" s="0">
-        <v>54100.0</v>
+        <v>56400.0</v>
+      </c>
+      <c r="X12" t="n" s="0">
+        <v>42070.0</v>
       </c>
     </row>
     <row r="13">
@@ -1015,64 +1054,67 @@
         <v>1000.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>57200.0</v>
+        <v>93900.0</v>
       </c>
       <c r="E13" t="n" s="0">
-        <v>92300.0</v>
+        <v>76800.0</v>
       </c>
       <c r="F13" t="n" s="0">
-        <v>56400.0</v>
+        <v>259500.0</v>
       </c>
       <c r="G13" t="n" s="0">
-        <v>35900.0</v>
+        <v>68900.0</v>
       </c>
       <c r="H13" t="n" s="0">
-        <v>36500.0</v>
+        <v>39500.0</v>
       </c>
       <c r="I13" t="n" s="0">
-        <v>75600.0</v>
+        <v>5194800.0</v>
       </c>
       <c r="J13" t="n" s="0">
-        <v>42300.0</v>
+        <v>39100.0</v>
       </c>
       <c r="K13" t="n" s="0">
-        <v>56200.0</v>
+        <v>38400.0</v>
       </c>
       <c r="L13" t="n" s="0">
-        <v>41400.0</v>
+        <v>40200.0</v>
       </c>
       <c r="M13" t="n" s="0">
-        <v>37300.0</v>
+        <v>91200.0</v>
       </c>
       <c r="N13" t="n" s="0">
-        <v>60000.0</v>
+        <v>89000.0</v>
       </c>
       <c r="O13" t="n" s="0">
-        <v>55500.0</v>
+        <v>52700.0</v>
       </c>
       <c r="P13" t="n" s="0">
-        <v>35500.0</v>
+        <v>36900.0</v>
       </c>
       <c r="Q13" t="n" s="0">
-        <v>75900.0</v>
+        <v>39500.0</v>
       </c>
       <c r="R13" t="n" s="0">
-        <v>37300.0</v>
+        <v>46100.0</v>
       </c>
       <c r="S13" t="n" s="0">
-        <v>45200.0</v>
+        <v>61900.0</v>
       </c>
       <c r="T13" t="n" s="0">
-        <v>35100.0</v>
+        <v>36000.0</v>
       </c>
       <c r="U13" t="n" s="0">
-        <v>64900.0</v>
+        <v>43900.0</v>
       </c>
       <c r="V13" t="n" s="0">
-        <v>47600.0</v>
+        <v>40100.0</v>
       </c>
       <c r="W13" t="n" s="0">
-        <v>80300.0</v>
+        <v>84200.0</v>
+      </c>
+      <c r="X13" t="n" s="0">
+        <v>323630.0</v>
       </c>
     </row>
     <row r="14">
@@ -1086,64 +1128,67 @@
         <v>1000.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>125200.0</v>
+        <v>172000.0</v>
       </c>
       <c r="E14" t="n" s="0">
-        <v>185300.0</v>
+        <v>148300.0</v>
       </c>
       <c r="F14" t="n" s="0">
-        <v>177600.0</v>
+        <v>158900.0</v>
       </c>
       <c r="G14" t="n" s="0">
-        <v>116600.0</v>
+        <v>150500.0</v>
       </c>
       <c r="H14" t="n" s="0">
-        <v>110900.0</v>
+        <v>269600.0</v>
       </c>
       <c r="I14" t="n" s="0">
-        <v>139900.0</v>
+        <v>119900.0</v>
       </c>
       <c r="J14" t="n" s="0">
-        <v>175400.0</v>
+        <v>150100.0</v>
       </c>
       <c r="K14" t="n" s="0">
-        <v>123200.0</v>
+        <v>98200.0</v>
       </c>
       <c r="L14" t="n" s="0">
-        <v>101800.0</v>
+        <v>104400.0</v>
       </c>
       <c r="M14" t="n" s="0">
-        <v>99300.0</v>
+        <v>105200.0</v>
       </c>
       <c r="N14" t="n" s="0">
-        <v>122900.0</v>
+        <v>153300.0</v>
       </c>
       <c r="O14" t="n" s="0">
-        <v>119300.0</v>
+        <v>157700.0</v>
       </c>
       <c r="P14" t="n" s="0">
-        <v>93100.0</v>
+        <v>96000.0</v>
       </c>
       <c r="Q14" t="n" s="0">
-        <v>137600.0</v>
+        <v>97300.0</v>
       </c>
       <c r="R14" t="n" s="0">
-        <v>96100.0</v>
+        <v>96800.0</v>
       </c>
       <c r="S14" t="n" s="0">
-        <v>102100.0</v>
+        <v>96600.0</v>
       </c>
       <c r="T14" t="n" s="0">
-        <v>96200.0</v>
+        <v>95500.0</v>
       </c>
       <c r="U14" t="n" s="0">
-        <v>130900.0</v>
+        <v>100900.0</v>
       </c>
       <c r="V14" t="n" s="0">
-        <v>97900.0</v>
+        <v>103500.0</v>
       </c>
       <c r="W14" t="n" s="0">
-        <v>151200.0</v>
+        <v>149500.0</v>
+      </c>
+      <c r="X14" t="n" s="0">
+        <v>131210.0</v>
       </c>
     </row>
     <row r="15">
@@ -1157,64 +1202,67 @@
         <v>1000.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>57500.0</v>
+        <v>97600.0</v>
       </c>
       <c r="E15" t="n" s="0">
-        <v>100000.0</v>
+        <v>97300.0</v>
       </c>
       <c r="F15" t="n" s="0">
-        <v>99800.0</v>
+        <v>99600.0</v>
       </c>
       <c r="G15" t="n" s="0">
-        <v>51400.0</v>
+        <v>66100.0</v>
       </c>
       <c r="H15" t="n" s="0">
-        <v>97100.0</v>
+        <v>91300.0</v>
       </c>
       <c r="I15" t="n" s="0">
-        <v>85400.0</v>
+        <v>67600.0</v>
       </c>
       <c r="J15" t="n" s="0">
-        <v>57800.0</v>
+        <v>86000.0</v>
       </c>
       <c r="K15" t="n" s="0">
-        <v>79600.0</v>
+        <v>54100.0</v>
       </c>
       <c r="L15" t="n" s="0">
-        <v>43800.0</v>
+        <v>51100.0</v>
       </c>
       <c r="M15" t="n" s="0">
-        <v>45000.0</v>
+        <v>49100.0</v>
       </c>
       <c r="N15" t="n" s="0">
-        <v>69600.0</v>
+        <v>77200.0</v>
       </c>
       <c r="O15" t="n" s="0">
-        <v>61700.0</v>
+        <v>71300.0</v>
       </c>
       <c r="P15" t="n" s="0">
-        <v>46900.0</v>
+        <v>55500.0</v>
       </c>
       <c r="Q15" t="n" s="0">
-        <v>85700.0</v>
+        <v>47700.0</v>
       </c>
       <c r="R15" t="n" s="0">
-        <v>47400.0</v>
+        <v>53800.0</v>
       </c>
       <c r="S15" t="n" s="0">
-        <v>42100.0</v>
+        <v>47000.0</v>
       </c>
       <c r="T15" t="n" s="0">
-        <v>49000.0</v>
+        <v>48800.0</v>
       </c>
       <c r="U15" t="n" s="0">
-        <v>100100.0</v>
+        <v>48600.0</v>
       </c>
       <c r="V15" t="n" s="0">
-        <v>51400.0</v>
+        <v>50300.0</v>
       </c>
       <c r="W15" t="n" s="0">
-        <v>92100.0</v>
+        <v>86800.0</v>
+      </c>
+      <c r="X15" t="n" s="0">
+        <v>67340.0</v>
       </c>
     </row>
     <row r="16">
@@ -1228,64 +1276,67 @@
         <v>1000.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>134300.0</v>
+        <v>125200.0</v>
       </c>
       <c r="E16" t="n" s="0">
-        <v>145200.0</v>
+        <v>97700.0</v>
       </c>
       <c r="F16" t="n" s="0">
-        <v>98200.0</v>
+        <v>62300.0</v>
       </c>
       <c r="G16" t="n" s="0">
-        <v>62400.0</v>
+        <v>104600.0</v>
       </c>
       <c r="H16" t="n" s="0">
-        <v>52400.0</v>
+        <v>107000.0</v>
       </c>
       <c r="I16" t="n" s="0">
-        <v>92200.0</v>
+        <v>63200.0</v>
       </c>
       <c r="J16" t="n" s="0">
-        <v>50400.0</v>
+        <v>60500.0</v>
       </c>
       <c r="K16" t="n" s="0">
-        <v>53600.0</v>
+        <v>44500.0</v>
       </c>
       <c r="L16" t="n" s="0">
-        <v>49000.0</v>
+        <v>46700.0</v>
       </c>
       <c r="M16" t="n" s="0">
-        <v>55100.0</v>
+        <v>46400.0</v>
       </c>
       <c r="N16" t="n" s="0">
-        <v>67500.0</v>
+        <v>52200.0</v>
       </c>
       <c r="O16" t="n" s="0">
-        <v>51900.0</v>
+        <v>94200.0</v>
       </c>
       <c r="P16" t="n" s="0">
-        <v>44400.0</v>
+        <v>50900.0</v>
       </c>
       <c r="Q16" t="n" s="0">
-        <v>93100.0</v>
+        <v>44500.0</v>
       </c>
       <c r="R16" t="n" s="0">
-        <v>46400.0</v>
+        <v>60400.0</v>
       </c>
       <c r="S16" t="n" s="0">
-        <v>47800.0</v>
+        <v>44100.0</v>
       </c>
       <c r="T16" t="n" s="0">
-        <v>42400.0</v>
+        <v>51500.0</v>
       </c>
       <c r="U16" t="n" s="0">
-        <v>69200.0</v>
+        <v>44700.0</v>
       </c>
       <c r="V16" t="n" s="0">
-        <v>45800.0</v>
+        <v>116700.0</v>
       </c>
       <c r="W16" t="n" s="0">
-        <v>94500.0</v>
+        <v>83400.0</v>
+      </c>
+      <c r="X16" t="n" s="0">
+        <v>70035.0</v>
       </c>
     </row>
   </sheetData>
